--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1597,6 +1597,1865 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120117039</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78560</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>185</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>759732</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7093922</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120117299</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57463</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>759645</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7094007</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120116927</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57679</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>759991</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7093717</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120116985</v>
+      </c>
+      <c r="B13" t="n">
+        <v>4766</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>759806</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7093910</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120116948</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8421</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>759991</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7093717</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120117321</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>759730</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7094006</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120117216</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57679</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>759669</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7093972</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120117695</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90527</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>759692</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7094117</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120117422</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>759709</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7094089</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120116996</v>
+      </c>
+      <c r="B19" t="n">
+        <v>4766</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>759799</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7093877</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120117092</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78560</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>185</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>759688</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7093898</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120117175</v>
+      </c>
+      <c r="B21" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>759658</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7093955</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120117023</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78560</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>185</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>759748</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7094005</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120116961</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97824</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>759818</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7093876</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120117194</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>759658</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7093955</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120117729</v>
+      </c>
+      <c r="B25" t="n">
+        <v>5189</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>759692</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7094117</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120117228</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57679</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>759719</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7093964</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -1599,10 +1599,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120117039</v>
+        <v>120117422</v>
       </c>
       <c r="B10" t="n">
-        <v>78560</v>
+        <v>57326</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,26 +1615,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1642,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759732</v>
+        <v>759709</v>
       </c>
       <c r="R10" t="n">
-        <v>7093922</v>
+        <v>7094089</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1672,12 +1677,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,7 +1691,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1705,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120117299</v>
+        <v>120117175</v>
       </c>
       <c r="B11" t="n">
-        <v>57463</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,27 +1725,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1749,10 +1752,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759645</v>
+        <v>759658</v>
       </c>
       <c r="R11" t="n">
-        <v>7094007</v>
+        <v>7093955</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1793,6 +1796,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1811,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120116927</v>
+        <v>120117695</v>
       </c>
       <c r="B12" t="n">
-        <v>57679</v>
+        <v>90527</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1827,27 +1831,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1855,10 +1858,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759991</v>
+        <v>759692</v>
       </c>
       <c r="R12" t="n">
-        <v>7093717</v>
+        <v>7094117</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1885,12 +1888,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,6 +1902,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1917,10 +1921,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120116985</v>
+        <v>120117321</v>
       </c>
       <c r="B13" t="n">
-        <v>4766</v>
+        <v>57326</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1929,34 +1933,33 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1966,10 +1969,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759806</v>
+        <v>759730</v>
       </c>
       <c r="R13" t="n">
-        <v>7093910</v>
+        <v>7094006</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1996,12 +1999,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2010,7 +2013,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2029,10 +2031,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120116948</v>
+        <v>120116996</v>
       </c>
       <c r="B14" t="n">
-        <v>8421</v>
+        <v>4766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2045,21 +2047,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>100299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2078,10 +2080,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759991</v>
+        <v>759799</v>
       </c>
       <c r="R14" t="n">
-        <v>7093717</v>
+        <v>7093877</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2125,26 +2127,6 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2161,10 +2143,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120117321</v>
+        <v>120117039</v>
       </c>
       <c r="B15" t="n">
-        <v>57326</v>
+        <v>78560</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2177,31 +2159,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2209,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>759730</v>
+        <v>759732</v>
       </c>
       <c r="R15" t="n">
-        <v>7094006</v>
+        <v>7093922</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2239,12 +2216,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2253,6 +2230,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2271,10 +2249,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120117216</v>
+        <v>120117194</v>
       </c>
       <c r="B16" t="n">
-        <v>57679</v>
+        <v>57326</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2283,20 +2261,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2307,7 +2285,11 @@
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2315,10 +2297,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759669</v>
+        <v>759658</v>
       </c>
       <c r="R16" t="n">
-        <v>7093972</v>
+        <v>7093955</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2377,10 +2359,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120117695</v>
+        <v>120117092</v>
       </c>
       <c r="B17" t="n">
-        <v>90527</v>
+        <v>78560</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2389,25 +2371,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2420,10 +2402,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759692</v>
+        <v>759688</v>
       </c>
       <c r="R17" t="n">
-        <v>7094117</v>
+        <v>7093898</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2483,10 +2465,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120117422</v>
+        <v>120117023</v>
       </c>
       <c r="B18" t="n">
-        <v>57326</v>
+        <v>78560</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2499,31 +2481,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2531,10 +2508,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759709</v>
+        <v>759748</v>
       </c>
       <c r="R18" t="n">
-        <v>7094089</v>
+        <v>7094005</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2561,12 +2538,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2575,6 +2552,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2593,10 +2571,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120116996</v>
+        <v>120117299</v>
       </c>
       <c r="B19" t="n">
-        <v>4766</v>
+        <v>57463</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2605,36 +2583,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100299</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2642,10 +2615,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759799</v>
+        <v>759645</v>
       </c>
       <c r="R19" t="n">
-        <v>7093877</v>
+        <v>7094007</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2672,12 +2645,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2686,7 +2659,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2705,10 +2677,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120117092</v>
+        <v>120116948</v>
       </c>
       <c r="B20" t="n">
-        <v>78560</v>
+        <v>8421</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2717,30 +2689,36 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>106554</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2748,10 +2726,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759688</v>
+        <v>759991</v>
       </c>
       <c r="R20" t="n">
-        <v>7093898</v>
+        <v>7093717</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2778,12 +2756,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2795,6 +2773,26 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2811,10 +2809,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120117175</v>
+        <v>120116985</v>
       </c>
       <c r="B21" t="n">
-        <v>90580</v>
+        <v>4766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2823,30 +2821,36 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2854,10 +2858,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759658</v>
+        <v>759806</v>
       </c>
       <c r="R21" t="n">
-        <v>7093955</v>
+        <v>7093910</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2884,12 +2888,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2917,10 +2921,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120117023</v>
+        <v>120116961</v>
       </c>
       <c r="B22" t="n">
-        <v>78560</v>
+        <v>97824</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2929,30 +2933,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>219790</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2960,10 +2965,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759748</v>
+        <v>759818</v>
       </c>
       <c r="R22" t="n">
-        <v>7094005</v>
+        <v>7093876</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2990,12 +2995,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3023,10 +3028,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120116961</v>
+        <v>120117228</v>
       </c>
       <c r="B23" t="n">
-        <v>97824</v>
+        <v>57679</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3039,27 +3044,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219790</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3067,10 +3072,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759818</v>
+        <v>759719</v>
       </c>
       <c r="R23" t="n">
-        <v>7093876</v>
+        <v>7093964</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3111,7 +3116,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3130,10 +3134,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120117194</v>
+        <v>120116927</v>
       </c>
       <c r="B24" t="n">
-        <v>57326</v>
+        <v>57679</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3142,20 +3146,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3166,11 +3170,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759658</v>
+        <v>759991</v>
       </c>
       <c r="R24" t="n">
-        <v>7093955</v>
+        <v>7093717</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3208,12 +3208,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3240,10 +3240,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120117729</v>
+        <v>120117216</v>
       </c>
       <c r="B25" t="n">
-        <v>5189</v>
+        <v>57679</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3256,16 +3256,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3274,14 +3274,9 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3289,10 +3284,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759692</v>
+        <v>759669</v>
       </c>
       <c r="R25" t="n">
-        <v>7094117</v>
+        <v>7093972</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3333,7 +3328,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3352,10 +3346,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120117228</v>
+        <v>120117729</v>
       </c>
       <c r="B26" t="n">
-        <v>57679</v>
+        <v>5189</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3368,16 +3362,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>105930</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3386,9 +3380,14 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3396,10 +3395,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759719</v>
+        <v>759692</v>
       </c>
       <c r="R26" t="n">
-        <v>7093964</v>
+        <v>7094117</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3440,6 +3439,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -1599,10 +1599,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120117422</v>
+        <v>120117023</v>
       </c>
       <c r="B10" t="n">
-        <v>57326</v>
+        <v>78560</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,31 +1615,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1647,10 +1642,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759709</v>
+        <v>759748</v>
       </c>
       <c r="R10" t="n">
-        <v>7094089</v>
+        <v>7094005</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1677,12 +1672,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1691,6 +1686,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1709,10 +1705,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120117175</v>
+        <v>120117729</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>5189</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,30 +1717,36 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1752,10 +1754,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759658</v>
+        <v>759692</v>
       </c>
       <c r="R11" t="n">
-        <v>7093955</v>
+        <v>7094117</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1815,10 +1817,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120117695</v>
+        <v>120117194</v>
       </c>
       <c r="B12" t="n">
-        <v>90527</v>
+        <v>57326</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1827,30 +1829,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1858,10 +1865,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759692</v>
+        <v>759658</v>
       </c>
       <c r="R12" t="n">
-        <v>7094117</v>
+        <v>7093955</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1902,7 +1909,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2031,10 +2037,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120116996</v>
+        <v>120116948</v>
       </c>
       <c r="B14" t="n">
-        <v>4766</v>
+        <v>8421</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2047,21 +2053,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100299</v>
+        <v>106554</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2080,10 +2086,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759799</v>
+        <v>759991</v>
       </c>
       <c r="R14" t="n">
-        <v>7093877</v>
+        <v>7093717</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2127,6 +2133,26 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2143,10 +2169,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120117039</v>
+        <v>120117216</v>
       </c>
       <c r="B15" t="n">
-        <v>78560</v>
+        <v>57679</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2155,30 +2181,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2186,10 +2213,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>759732</v>
+        <v>759669</v>
       </c>
       <c r="R15" t="n">
-        <v>7093922</v>
+        <v>7093972</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2216,12 +2243,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,7 +2257,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2249,10 +2275,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120117194</v>
+        <v>120117175</v>
       </c>
       <c r="B16" t="n">
-        <v>57326</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2265,31 +2291,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2341,6 +2362,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2359,10 +2381,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120117092</v>
+        <v>120117228</v>
       </c>
       <c r="B17" t="n">
-        <v>78560</v>
+        <v>57679</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,30 +2393,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2402,10 +2425,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759688</v>
+        <v>759719</v>
       </c>
       <c r="R17" t="n">
-        <v>7093898</v>
+        <v>7093964</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2446,7 +2469,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2465,10 +2487,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120117023</v>
+        <v>120117299</v>
       </c>
       <c r="B18" t="n">
-        <v>78560</v>
+        <v>57463</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2481,26 +2503,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2508,10 +2531,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759748</v>
+        <v>759645</v>
       </c>
       <c r="R18" t="n">
-        <v>7094005</v>
+        <v>7094007</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2538,12 +2561,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2552,7 +2575,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2571,10 +2593,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120117299</v>
+        <v>120116961</v>
       </c>
       <c r="B19" t="n">
-        <v>57463</v>
+        <v>97824</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2583,31 +2605,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2615,10 +2637,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759645</v>
+        <v>759818</v>
       </c>
       <c r="R19" t="n">
-        <v>7094007</v>
+        <v>7093876</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2659,6 +2681,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2677,10 +2700,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120116948</v>
+        <v>120117039</v>
       </c>
       <c r="B20" t="n">
-        <v>8421</v>
+        <v>78560</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2689,36 +2712,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106554</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2726,10 +2743,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759991</v>
+        <v>759732</v>
       </c>
       <c r="R20" t="n">
-        <v>7093717</v>
+        <v>7093922</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2773,26 +2790,6 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2809,10 +2806,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120116985</v>
+        <v>120116927</v>
       </c>
       <c r="B21" t="n">
-        <v>4766</v>
+        <v>57679</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2825,32 +2822,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100299</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2858,10 +2850,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759806</v>
+        <v>759991</v>
       </c>
       <c r="R21" t="n">
-        <v>7093910</v>
+        <v>7093717</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2902,7 +2894,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2921,10 +2912,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120116961</v>
+        <v>120116996</v>
       </c>
       <c r="B22" t="n">
-        <v>97824</v>
+        <v>4766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2937,27 +2928,32 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219790</v>
+        <v>100299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2965,10 +2961,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759818</v>
+        <v>759799</v>
       </c>
       <c r="R22" t="n">
-        <v>7093876</v>
+        <v>7093877</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2995,12 +2991,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3028,10 +3024,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120117228</v>
+        <v>120117695</v>
       </c>
       <c r="B23" t="n">
-        <v>57679</v>
+        <v>90527</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3044,27 +3040,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3072,10 +3067,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759719</v>
+        <v>759692</v>
       </c>
       <c r="R23" t="n">
-        <v>7093964</v>
+        <v>7094117</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3116,6 +3111,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3134,10 +3130,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120116927</v>
+        <v>120116985</v>
       </c>
       <c r="B24" t="n">
-        <v>57679</v>
+        <v>4766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3150,27 +3146,32 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>100299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3178,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759991</v>
+        <v>759806</v>
       </c>
       <c r="R24" t="n">
-        <v>7093717</v>
+        <v>7093910</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3222,6 +3223,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3240,10 +3242,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120117216</v>
+        <v>120117092</v>
       </c>
       <c r="B25" t="n">
-        <v>57679</v>
+        <v>78560</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3252,31 +3254,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3284,10 +3285,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759669</v>
+        <v>759688</v>
       </c>
       <c r="R25" t="n">
-        <v>7093972</v>
+        <v>7093898</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3328,6 +3329,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3346,10 +3348,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120117729</v>
+        <v>120117422</v>
       </c>
       <c r="B26" t="n">
-        <v>5189</v>
+        <v>57326</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3358,20 +3360,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3380,12 +3382,11 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3395,10 +3396,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759692</v>
+        <v>759709</v>
       </c>
       <c r="R26" t="n">
-        <v>7094117</v>
+        <v>7094089</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3439,7 +3440,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -2700,10 +2700,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120117039</v>
+        <v>120116927</v>
       </c>
       <c r="B20" t="n">
-        <v>78560</v>
+        <v>57679</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2712,30 +2712,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2743,10 +2744,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759732</v>
+        <v>759991</v>
       </c>
       <c r="R20" t="n">
-        <v>7093922</v>
+        <v>7093717</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2787,7 +2788,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2806,10 +2806,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120116927</v>
+        <v>120117039</v>
       </c>
       <c r="B21" t="n">
-        <v>57679</v>
+        <v>78560</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2818,31 +2818,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2850,10 +2849,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759991</v>
+        <v>759732</v>
       </c>
       <c r="R21" t="n">
-        <v>7093717</v>
+        <v>7093922</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2894,6 +2893,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -2700,10 +2700,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120116927</v>
+        <v>120117039</v>
       </c>
       <c r="B20" t="n">
-        <v>57679</v>
+        <v>78560</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2712,31 +2712,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2744,10 +2743,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759991</v>
+        <v>759732</v>
       </c>
       <c r="R20" t="n">
-        <v>7093717</v>
+        <v>7093922</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2788,6 +2787,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2806,10 +2806,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120117039</v>
+        <v>120116927</v>
       </c>
       <c r="B21" t="n">
-        <v>78560</v>
+        <v>57679</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2818,30 +2818,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2849,10 +2850,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759732</v>
+        <v>759991</v>
       </c>
       <c r="R21" t="n">
-        <v>7093922</v>
+        <v>7093717</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2893,7 +2894,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -1599,10 +1599,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120117023</v>
+        <v>120117039</v>
       </c>
       <c r="B10" t="n">
-        <v>78560</v>
+        <v>78576</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759748</v>
+        <v>759732</v>
       </c>
       <c r="R10" t="n">
-        <v>7094005</v>
+        <v>7093922</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120117729</v>
+        <v>120117228</v>
       </c>
       <c r="B11" t="n">
-        <v>5189</v>
+        <v>57689</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,16 +1721,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1739,14 +1739,9 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1754,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759692</v>
+        <v>759719</v>
       </c>
       <c r="R11" t="n">
-        <v>7094117</v>
+        <v>7093964</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1798,7 +1793,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1817,10 +1811,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120117194</v>
+        <v>120117729</v>
       </c>
       <c r="B12" t="n">
-        <v>57326</v>
+        <v>5189</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,20 +1823,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1851,11 +1845,12 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1865,10 +1860,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759658</v>
+        <v>759692</v>
       </c>
       <c r="R12" t="n">
-        <v>7093955</v>
+        <v>7094117</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1909,6 +1904,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1927,10 +1923,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120117321</v>
+        <v>120117194</v>
       </c>
       <c r="B13" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1975,10 +1971,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759730</v>
+        <v>759658</v>
       </c>
       <c r="R13" t="n">
-        <v>7094006</v>
+        <v>7093955</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2169,10 +2165,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120117216</v>
+        <v>120116961</v>
       </c>
       <c r="B15" t="n">
-        <v>57679</v>
+        <v>97847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2185,27 +2181,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2213,10 +2209,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>759669</v>
+        <v>759818</v>
       </c>
       <c r="R15" t="n">
-        <v>7093972</v>
+        <v>7093876</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2257,6 +2253,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2275,10 +2272,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120117175</v>
+        <v>120117023</v>
       </c>
       <c r="B16" t="n">
-        <v>90580</v>
+        <v>78576</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2291,21 +2288,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2318,10 +2315,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759658</v>
+        <v>759748</v>
       </c>
       <c r="R16" t="n">
-        <v>7093955</v>
+        <v>7094005</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2348,12 +2345,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2381,10 +2378,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120117228</v>
+        <v>120117175</v>
       </c>
       <c r="B17" t="n">
-        <v>57679</v>
+        <v>90598</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2393,31 +2390,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2425,10 +2421,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759719</v>
+        <v>759658</v>
       </c>
       <c r="R17" t="n">
-        <v>7093964</v>
+        <v>7093955</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2469,6 +2465,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2487,10 +2484,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120117299</v>
+        <v>120117216</v>
       </c>
       <c r="B18" t="n">
-        <v>57463</v>
+        <v>57689</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2499,25 +2496,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2531,10 +2528,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759645</v>
+        <v>759669</v>
       </c>
       <c r="R18" t="n">
-        <v>7094007</v>
+        <v>7093972</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2593,10 +2590,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120116961</v>
+        <v>120116927</v>
       </c>
       <c r="B19" t="n">
-        <v>97824</v>
+        <v>57689</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2609,27 +2606,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2637,10 +2634,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759818</v>
+        <v>759991</v>
       </c>
       <c r="R19" t="n">
-        <v>7093876</v>
+        <v>7093717</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2667,12 +2664,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2681,7 +2678,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2700,10 +2696,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120116927</v>
+        <v>120116996</v>
       </c>
       <c r="B20" t="n">
-        <v>57679</v>
+        <v>4766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2716,27 +2712,32 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>100299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2744,10 +2745,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759991</v>
+        <v>759799</v>
       </c>
       <c r="R20" t="n">
-        <v>7093717</v>
+        <v>7093877</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2788,6 +2789,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2806,10 +2808,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120117039</v>
+        <v>120117092</v>
       </c>
       <c r="B21" t="n">
-        <v>78560</v>
+        <v>78576</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2849,10 +2851,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759732</v>
+        <v>759688</v>
       </c>
       <c r="R21" t="n">
-        <v>7093922</v>
+        <v>7093898</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2879,12 +2881,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2912,10 +2914,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120116996</v>
+        <v>120117695</v>
       </c>
       <c r="B22" t="n">
-        <v>4766</v>
+        <v>90545</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2928,32 +2930,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100299</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2961,10 +2957,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759799</v>
+        <v>759692</v>
       </c>
       <c r="R22" t="n">
-        <v>7093877</v>
+        <v>7094117</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2991,12 +2987,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3024,10 +3020,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120117695</v>
+        <v>120117422</v>
       </c>
       <c r="B23" t="n">
-        <v>90527</v>
+        <v>57336</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3036,30 +3032,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3067,10 +3068,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759692</v>
+        <v>759709</v>
       </c>
       <c r="R23" t="n">
-        <v>7094117</v>
+        <v>7094089</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3111,7 +3112,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120116985</v>
+        <v>120117299</v>
       </c>
       <c r="B24" t="n">
-        <v>4766</v>
+        <v>57473</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3142,36 +3142,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100299</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3179,10 +3174,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759806</v>
+        <v>759645</v>
       </c>
       <c r="R24" t="n">
-        <v>7093910</v>
+        <v>7094007</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3209,12 +3204,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3223,7 +3218,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3242,10 +3236,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120117092</v>
+        <v>120116985</v>
       </c>
       <c r="B25" t="n">
-        <v>78560</v>
+        <v>4766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3254,30 +3248,36 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>100299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3285,10 +3285,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759688</v>
+        <v>759806</v>
       </c>
       <c r="R25" t="n">
-        <v>7093898</v>
+        <v>7093910</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3315,12 +3315,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3348,10 +3348,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120117422</v>
+        <v>120117321</v>
       </c>
       <c r="B26" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3396,10 +3396,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759709</v>
+        <v>759730</v>
       </c>
       <c r="R26" t="n">
-        <v>7094089</v>
+        <v>7094006</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -1599,10 +1599,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120117039</v>
+        <v>120117194</v>
       </c>
       <c r="B10" t="n">
-        <v>78576</v>
+        <v>57336</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,26 +1615,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1642,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759732</v>
+        <v>759658</v>
       </c>
       <c r="R10" t="n">
-        <v>7093922</v>
+        <v>7093955</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1672,12 +1677,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,7 +1691,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1705,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120117228</v>
+        <v>120117092</v>
       </c>
       <c r="B11" t="n">
-        <v>57689</v>
+        <v>78576</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,31 +1721,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1749,10 +1752,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759719</v>
+        <v>759688</v>
       </c>
       <c r="R11" t="n">
-        <v>7093964</v>
+        <v>7093898</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1793,6 +1796,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1811,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120117729</v>
+        <v>120117175</v>
       </c>
       <c r="B12" t="n">
-        <v>5189</v>
+        <v>90598</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1823,36 +1827,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1860,10 +1858,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759692</v>
+        <v>759658</v>
       </c>
       <c r="R12" t="n">
-        <v>7094117</v>
+        <v>7093955</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1923,10 +1921,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120117194</v>
+        <v>120116985</v>
       </c>
       <c r="B13" t="n">
-        <v>57336</v>
+        <v>4766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1935,33 +1933,34 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1971,10 +1970,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759658</v>
+        <v>759806</v>
       </c>
       <c r="R13" t="n">
-        <v>7093955</v>
+        <v>7093910</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2001,12 +2000,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2015,6 +2014,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120116948</v>
+        <v>120117695</v>
       </c>
       <c r="B14" t="n">
-        <v>8421</v>
+        <v>90545</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2049,32 +2049,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2082,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759991</v>
+        <v>759692</v>
       </c>
       <c r="R14" t="n">
-        <v>7093717</v>
+        <v>7094117</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2112,12 +2106,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2129,26 +2123,6 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2165,10 +2139,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120116961</v>
+        <v>120117228</v>
       </c>
       <c r="B15" t="n">
-        <v>97847</v>
+        <v>57689</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2181,27 +2155,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2209,10 +2183,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>759818</v>
+        <v>759719</v>
       </c>
       <c r="R15" t="n">
-        <v>7093876</v>
+        <v>7093964</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2253,7 +2227,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2272,10 +2245,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120117023</v>
+        <v>120116961</v>
       </c>
       <c r="B16" t="n">
-        <v>78576</v>
+        <v>97847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2284,30 +2257,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>219790</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2315,10 +2289,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759748</v>
+        <v>759818</v>
       </c>
       <c r="R16" t="n">
-        <v>7094005</v>
+        <v>7093876</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2345,12 +2319,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2378,10 +2352,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120117175</v>
+        <v>120116948</v>
       </c>
       <c r="B17" t="n">
-        <v>90598</v>
+        <v>8421</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2390,30 +2364,36 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>106554</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2421,10 +2401,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759658</v>
+        <v>759991</v>
       </c>
       <c r="R17" t="n">
-        <v>7093955</v>
+        <v>7093717</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2451,12 +2431,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2468,6 +2448,26 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2484,10 +2484,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120117216</v>
+        <v>120117299</v>
       </c>
       <c r="B18" t="n">
-        <v>57689</v>
+        <v>57473</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2496,25 +2496,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2528,10 +2528,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759669</v>
+        <v>759645</v>
       </c>
       <c r="R18" t="n">
-        <v>7093972</v>
+        <v>7094007</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2590,10 +2590,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120116927</v>
+        <v>120117422</v>
       </c>
       <c r="B19" t="n">
-        <v>57689</v>
+        <v>57336</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2602,20 +2602,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2626,7 +2626,11 @@
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2634,10 +2638,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759991</v>
+        <v>759709</v>
       </c>
       <c r="R19" t="n">
-        <v>7093717</v>
+        <v>7094089</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2664,12 +2668,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2808,10 +2812,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120117092</v>
+        <v>120116927</v>
       </c>
       <c r="B21" t="n">
-        <v>78576</v>
+        <v>57689</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2820,30 +2824,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2851,10 +2856,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759688</v>
+        <v>759991</v>
       </c>
       <c r="R21" t="n">
-        <v>7093898</v>
+        <v>7093717</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2881,12 +2886,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2895,7 +2900,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2914,10 +2918,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120117695</v>
+        <v>120117321</v>
       </c>
       <c r="B22" t="n">
-        <v>90545</v>
+        <v>57336</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2926,30 +2930,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2957,10 +2966,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759692</v>
+        <v>759730</v>
       </c>
       <c r="R22" t="n">
-        <v>7094117</v>
+        <v>7094006</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3001,7 +3010,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3020,10 +3028,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120117422</v>
+        <v>120117216</v>
       </c>
       <c r="B23" t="n">
-        <v>57336</v>
+        <v>57689</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3032,20 +3040,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3056,11 +3064,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3068,10 +3072,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759709</v>
+        <v>759669</v>
       </c>
       <c r="R23" t="n">
-        <v>7094089</v>
+        <v>7093972</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3130,10 +3134,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120117299</v>
+        <v>120117023</v>
       </c>
       <c r="B24" t="n">
-        <v>57473</v>
+        <v>78576</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3146,27 +3150,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3174,10 +3177,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759645</v>
+        <v>759748</v>
       </c>
       <c r="R24" t="n">
-        <v>7094007</v>
+        <v>7094005</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3204,12 +3207,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3218,6 +3221,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3236,10 +3240,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120116985</v>
+        <v>120117729</v>
       </c>
       <c r="B25" t="n">
-        <v>4766</v>
+        <v>5189</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3252,21 +3256,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100299</v>
+        <v>105930</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3285,10 +3289,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759806</v>
+        <v>759692</v>
       </c>
       <c r="R25" t="n">
-        <v>7093910</v>
+        <v>7094117</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3315,12 +3319,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3348,10 +3352,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120117321</v>
+        <v>120117039</v>
       </c>
       <c r="B26" t="n">
-        <v>57336</v>
+        <v>78576</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3364,31 +3368,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3396,10 +3395,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759730</v>
+        <v>759732</v>
       </c>
       <c r="R26" t="n">
-        <v>7094006</v>
+        <v>7093922</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3426,12 +3425,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3440,6 +3439,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -1921,10 +1921,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120116985</v>
+        <v>120117695</v>
       </c>
       <c r="B13" t="n">
-        <v>4766</v>
+        <v>90545</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1937,32 +1937,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100299</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1970,10 +1964,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759806</v>
+        <v>759692</v>
       </c>
       <c r="R13" t="n">
-        <v>7093910</v>
+        <v>7094117</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2000,12 +1994,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2033,10 +2027,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120117695</v>
+        <v>120116985</v>
       </c>
       <c r="B14" t="n">
-        <v>90545</v>
+        <v>4766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2049,26 +2043,32 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>100299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759692</v>
+        <v>759806</v>
       </c>
       <c r="R14" t="n">
-        <v>7094117</v>
+        <v>7093910</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2352,10 +2352,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120116948</v>
+        <v>120117299</v>
       </c>
       <c r="B17" t="n">
-        <v>8421</v>
+        <v>57473</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2364,36 +2364,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2401,10 +2396,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759991</v>
+        <v>759645</v>
       </c>
       <c r="R17" t="n">
-        <v>7093717</v>
+        <v>7094007</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2431,12 +2426,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2445,29 +2440,8 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2484,10 +2458,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120117299</v>
+        <v>120116948</v>
       </c>
       <c r="B18" t="n">
-        <v>57473</v>
+        <v>8421</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2496,31 +2470,36 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2528,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759645</v>
+        <v>759991</v>
       </c>
       <c r="R18" t="n">
-        <v>7094007</v>
+        <v>7093717</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2558,12 +2537,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2572,8 +2551,29 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2812,10 +2812,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120116927</v>
+        <v>120117321</v>
       </c>
       <c r="B21" t="n">
-        <v>57689</v>
+        <v>57336</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2824,20 +2824,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2848,7 +2848,11 @@
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2856,10 +2860,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759991</v>
+        <v>759730</v>
       </c>
       <c r="R21" t="n">
-        <v>7093717</v>
+        <v>7094006</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2886,12 +2890,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2918,10 +2922,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120117321</v>
+        <v>120116927</v>
       </c>
       <c r="B22" t="n">
-        <v>57336</v>
+        <v>57689</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2930,20 +2934,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2954,11 +2958,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759730</v>
+        <v>759991</v>
       </c>
       <c r="R22" t="n">
-        <v>7094006</v>
+        <v>7093717</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2996,12 +2996,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3134,10 +3134,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120117023</v>
+        <v>120117729</v>
       </c>
       <c r="B24" t="n">
-        <v>78576</v>
+        <v>5189</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3146,30 +3146,36 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>105930</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3177,10 +3183,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759748</v>
+        <v>759692</v>
       </c>
       <c r="R24" t="n">
-        <v>7094005</v>
+        <v>7094117</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3207,12 +3213,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3240,10 +3246,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120117729</v>
+        <v>120117023</v>
       </c>
       <c r="B25" t="n">
-        <v>5189</v>
+        <v>78576</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3252,36 +3258,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>105930</v>
+        <v>185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759692</v>
+        <v>759748</v>
       </c>
       <c r="R25" t="n">
-        <v>7094117</v>
+        <v>7094005</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3319,12 +3319,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -1599,10 +1599,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120117194</v>
+        <v>120117695</v>
       </c>
       <c r="B10" t="n">
-        <v>57336</v>
+        <v>90545</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,35 +1611,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1647,10 +1642,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759658</v>
+        <v>759692</v>
       </c>
       <c r="R10" t="n">
-        <v>7093955</v>
+        <v>7094117</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1691,6 +1686,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1709,10 +1705,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120117092</v>
+        <v>120116961</v>
       </c>
       <c r="B11" t="n">
-        <v>78576</v>
+        <v>97847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,30 +1717,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1752,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759688</v>
+        <v>759818</v>
       </c>
       <c r="R11" t="n">
-        <v>7093898</v>
+        <v>7093876</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1815,10 +1812,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120117175</v>
+        <v>120117321</v>
       </c>
       <c r="B12" t="n">
-        <v>90598</v>
+        <v>57336</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,26 +1828,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1858,10 +1860,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759658</v>
+        <v>759730</v>
       </c>
       <c r="R12" t="n">
-        <v>7093955</v>
+        <v>7094006</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1902,7 +1904,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1921,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120117695</v>
+        <v>120117228</v>
       </c>
       <c r="B13" t="n">
-        <v>90545</v>
+        <v>57689</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1937,26 +1938,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1964,10 +1966,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759692</v>
+        <v>759719</v>
       </c>
       <c r="R13" t="n">
-        <v>7094117</v>
+        <v>7093964</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2008,7 +2010,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2027,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120116985</v>
+        <v>120117729</v>
       </c>
       <c r="B14" t="n">
-        <v>4766</v>
+        <v>5189</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2043,21 +2044,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100299</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2076,10 +2077,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759806</v>
+        <v>759692</v>
       </c>
       <c r="R14" t="n">
-        <v>7093910</v>
+        <v>7094117</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2106,12 +2107,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2139,10 +2140,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120117228</v>
+        <v>120116948</v>
       </c>
       <c r="B15" t="n">
-        <v>57689</v>
+        <v>8421</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2155,27 +2156,32 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>106554</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2183,10 +2189,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>759719</v>
+        <v>759991</v>
       </c>
       <c r="R15" t="n">
-        <v>7093964</v>
+        <v>7093717</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2213,12 +2219,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2227,8 +2233,29 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2245,10 +2272,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120116961</v>
+        <v>120117039</v>
       </c>
       <c r="B16" t="n">
-        <v>97847</v>
+        <v>78576</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2257,31 +2284,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2289,10 +2315,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759818</v>
+        <v>759732</v>
       </c>
       <c r="R16" t="n">
-        <v>7093876</v>
+        <v>7093922</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2319,12 +2345,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2352,10 +2378,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120117299</v>
+        <v>120116985</v>
       </c>
       <c r="B17" t="n">
-        <v>57473</v>
+        <v>4766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2364,31 +2390,36 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2396,10 +2427,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759645</v>
+        <v>759806</v>
       </c>
       <c r="R17" t="n">
-        <v>7094007</v>
+        <v>7093910</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2426,12 +2457,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2440,6 +2471,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2458,10 +2490,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120116948</v>
+        <v>120117194</v>
       </c>
       <c r="B18" t="n">
-        <v>8421</v>
+        <v>57336</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2470,34 +2502,33 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2507,10 +2538,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759991</v>
+        <v>759658</v>
       </c>
       <c r="R18" t="n">
-        <v>7093717</v>
+        <v>7093955</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2537,12 +2568,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2551,29 +2582,8 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2590,10 +2600,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120117422</v>
+        <v>120117299</v>
       </c>
       <c r="B19" t="n">
-        <v>57336</v>
+        <v>57473</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2606,31 +2616,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2638,10 +2644,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759709</v>
+        <v>759645</v>
       </c>
       <c r="R19" t="n">
-        <v>7094089</v>
+        <v>7094007</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2700,10 +2706,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120116996</v>
+        <v>120117023</v>
       </c>
       <c r="B20" t="n">
-        <v>4766</v>
+        <v>78576</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2712,36 +2718,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100299</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2749,10 +2749,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759799</v>
+        <v>759748</v>
       </c>
       <c r="R20" t="n">
-        <v>7093877</v>
+        <v>7094005</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2812,7 +2812,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120117321</v>
+        <v>120117422</v>
       </c>
       <c r="B21" t="n">
         <v>57336</v>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759730</v>
+        <v>759709</v>
       </c>
       <c r="R21" t="n">
-        <v>7094006</v>
+        <v>7094089</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2922,10 +2922,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120116927</v>
+        <v>120117092</v>
       </c>
       <c r="B22" t="n">
-        <v>57689</v>
+        <v>78576</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2934,31 +2934,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2966,10 +2965,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759991</v>
+        <v>759688</v>
       </c>
       <c r="R22" t="n">
-        <v>7093717</v>
+        <v>7093898</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2996,12 +2995,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3010,6 +3009,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3028,7 +3028,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120117216</v>
+        <v>120116927</v>
       </c>
       <c r="B23" t="n">
         <v>57689</v>
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759669</v>
+        <v>759991</v>
       </c>
       <c r="R23" t="n">
-        <v>7093972</v>
+        <v>7093717</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3102,12 +3102,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3134,10 +3134,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120117729</v>
+        <v>120117216</v>
       </c>
       <c r="B24" t="n">
-        <v>5189</v>
+        <v>57689</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3150,16 +3150,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3168,14 +3168,9 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3183,10 +3178,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759692</v>
+        <v>759669</v>
       </c>
       <c r="R24" t="n">
-        <v>7094117</v>
+        <v>7093972</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3227,7 +3222,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3246,10 +3240,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120117023</v>
+        <v>120117175</v>
       </c>
       <c r="B25" t="n">
-        <v>78576</v>
+        <v>90598</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3262,21 +3256,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3289,10 +3283,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759748</v>
+        <v>759658</v>
       </c>
       <c r="R25" t="n">
-        <v>7094005</v>
+        <v>7093955</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3319,12 +3313,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3352,10 +3346,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120117039</v>
+        <v>120116996</v>
       </c>
       <c r="B26" t="n">
-        <v>78576</v>
+        <v>4766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3364,30 +3358,36 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>100299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3395,10 +3395,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759732</v>
+        <v>759799</v>
       </c>
       <c r="R26" t="n">
-        <v>7093922</v>
+        <v>7093877</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -2140,10 +2140,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120116948</v>
+        <v>120117039</v>
       </c>
       <c r="B15" t="n">
-        <v>8421</v>
+        <v>78576</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,36 +2152,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106554</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2189,10 +2183,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>759991</v>
+        <v>759732</v>
       </c>
       <c r="R15" t="n">
-        <v>7093717</v>
+        <v>7093922</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2236,26 +2230,6 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2272,10 +2246,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120117039</v>
+        <v>120116948</v>
       </c>
       <c r="B16" t="n">
-        <v>78576</v>
+        <v>8421</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2284,30 +2258,36 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>106554</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2315,10 +2295,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759732</v>
+        <v>759991</v>
       </c>
       <c r="R16" t="n">
-        <v>7093922</v>
+        <v>7093717</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2362,6 +2342,26 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2922,10 +2922,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120117092</v>
+        <v>120116927</v>
       </c>
       <c r="B22" t="n">
-        <v>78576</v>
+        <v>57689</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2934,30 +2934,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2965,10 +2966,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759688</v>
+        <v>759991</v>
       </c>
       <c r="R22" t="n">
-        <v>7093898</v>
+        <v>7093717</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2995,12 +2996,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3009,7 +3010,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120116927</v>
+        <v>120117092</v>
       </c>
       <c r="B23" t="n">
-        <v>57689</v>
+        <v>78576</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3040,31 +3040,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3072,10 +3071,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759991</v>
+        <v>759688</v>
       </c>
       <c r="R23" t="n">
-        <v>7093717</v>
+        <v>7093898</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3102,12 +3101,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3116,6 +3115,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -1599,10 +1599,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120117695</v>
+        <v>120116985</v>
       </c>
       <c r="B10" t="n">
-        <v>90545</v>
+        <v>4766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,26 +1615,32 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>100299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1642,10 +1648,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759692</v>
+        <v>759806</v>
       </c>
       <c r="R10" t="n">
-        <v>7094117</v>
+        <v>7093910</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1672,12 +1678,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1812,10 +1818,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120117321</v>
+        <v>120116996</v>
       </c>
       <c r="B12" t="n">
-        <v>57336</v>
+        <v>4766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1824,33 +1830,34 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1860,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759730</v>
+        <v>759799</v>
       </c>
       <c r="R12" t="n">
-        <v>7094006</v>
+        <v>7093877</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,12 +1897,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1904,6 +1911,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1922,10 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120117228</v>
+        <v>120117092</v>
       </c>
       <c r="B13" t="n">
-        <v>57689</v>
+        <v>78576</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1934,31 +1942,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1966,10 +1973,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759719</v>
+        <v>759688</v>
       </c>
       <c r="R13" t="n">
-        <v>7093964</v>
+        <v>7093898</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2010,6 +2017,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2028,10 +2036,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120117729</v>
+        <v>120117228</v>
       </c>
       <c r="B14" t="n">
-        <v>5189</v>
+        <v>57689</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2044,16 +2052,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2062,14 +2070,9 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2077,10 +2080,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759692</v>
+        <v>759719</v>
       </c>
       <c r="R14" t="n">
-        <v>7094117</v>
+        <v>7093964</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2121,7 +2124,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2140,10 +2142,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120117039</v>
+        <v>120116927</v>
       </c>
       <c r="B15" t="n">
-        <v>78576</v>
+        <v>57689</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,30 +2154,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2183,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>759732</v>
+        <v>759991</v>
       </c>
       <c r="R15" t="n">
-        <v>7093922</v>
+        <v>7093717</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2227,7 +2230,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2246,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120116948</v>
+        <v>120117194</v>
       </c>
       <c r="B16" t="n">
-        <v>8421</v>
+        <v>57336</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2258,34 +2260,33 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2295,10 +2296,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759991</v>
+        <v>759658</v>
       </c>
       <c r="R16" t="n">
-        <v>7093717</v>
+        <v>7093955</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2325,12 +2326,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2339,29 +2340,8 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2378,10 +2358,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120116985</v>
+        <v>120117023</v>
       </c>
       <c r="B17" t="n">
-        <v>4766</v>
+        <v>78576</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2390,36 +2370,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100299</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2427,10 +2401,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759806</v>
+        <v>759748</v>
       </c>
       <c r="R17" t="n">
-        <v>7093910</v>
+        <v>7094005</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2490,7 +2464,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120117194</v>
+        <v>120117321</v>
       </c>
       <c r="B18" t="n">
         <v>57336</v>
@@ -2538,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759658</v>
+        <v>759730</v>
       </c>
       <c r="R18" t="n">
-        <v>7093955</v>
+        <v>7094006</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2600,10 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120117299</v>
+        <v>120117422</v>
       </c>
       <c r="B19" t="n">
-        <v>57473</v>
+        <v>57336</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2616,27 +2590,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2644,10 +2622,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759645</v>
+        <v>759709</v>
       </c>
       <c r="R19" t="n">
-        <v>7094007</v>
+        <v>7094089</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2706,10 +2684,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120117023</v>
+        <v>120117729</v>
       </c>
       <c r="B20" t="n">
-        <v>78576</v>
+        <v>5189</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2718,30 +2696,36 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2749,10 +2733,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759748</v>
+        <v>759692</v>
       </c>
       <c r="R20" t="n">
-        <v>7094005</v>
+        <v>7094117</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2779,12 +2763,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2812,10 +2796,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120117422</v>
+        <v>120117216</v>
       </c>
       <c r="B21" t="n">
-        <v>57336</v>
+        <v>57689</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2824,20 +2808,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2848,11 +2832,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2860,10 +2840,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759709</v>
+        <v>759669</v>
       </c>
       <c r="R21" t="n">
-        <v>7094089</v>
+        <v>7093972</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2922,10 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120116927</v>
+        <v>120117039</v>
       </c>
       <c r="B22" t="n">
-        <v>57689</v>
+        <v>78576</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2934,31 +2914,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2966,10 +2945,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759991</v>
+        <v>759732</v>
       </c>
       <c r="R22" t="n">
-        <v>7093717</v>
+        <v>7093922</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3010,6 +2989,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3028,10 +3008,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120117092</v>
+        <v>120116948</v>
       </c>
       <c r="B23" t="n">
-        <v>78576</v>
+        <v>8421</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3040,30 +3020,36 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>106554</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3071,10 +3057,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759688</v>
+        <v>759991</v>
       </c>
       <c r="R23" t="n">
-        <v>7093898</v>
+        <v>7093717</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3101,12 +3087,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3118,6 +3104,26 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3134,10 +3140,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120117216</v>
+        <v>120117695</v>
       </c>
       <c r="B24" t="n">
-        <v>57689</v>
+        <v>90545</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3150,27 +3156,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3178,10 +3183,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759669</v>
+        <v>759692</v>
       </c>
       <c r="R24" t="n">
-        <v>7093972</v>
+        <v>7094117</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3222,6 +3227,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3240,10 +3246,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120117175</v>
+        <v>120117299</v>
       </c>
       <c r="B25" t="n">
-        <v>90598</v>
+        <v>57473</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3256,26 +3262,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3283,10 +3290,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759658</v>
+        <v>759645</v>
       </c>
       <c r="R25" t="n">
-        <v>7093955</v>
+        <v>7094007</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3327,7 +3334,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3346,10 +3352,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120116996</v>
+        <v>120117175</v>
       </c>
       <c r="B26" t="n">
-        <v>4766</v>
+        <v>90598</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3358,36 +3364,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100299</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3395,10 +3395,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759799</v>
+        <v>759658</v>
       </c>
       <c r="R26" t="n">
-        <v>7093877</v>
+        <v>7093955</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3425,12 +3425,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -1599,10 +1599,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120116985</v>
+        <v>120116948</v>
       </c>
       <c r="B10" t="n">
-        <v>4766</v>
+        <v>8421</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,21 +1615,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100299</v>
+        <v>106554</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759806</v>
+        <v>759991</v>
       </c>
       <c r="R10" t="n">
-        <v>7093910</v>
+        <v>7093717</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1695,6 +1695,26 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1711,10 +1731,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120116961</v>
+        <v>120117175</v>
       </c>
       <c r="B11" t="n">
-        <v>97847</v>
+        <v>90598</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,31 +1743,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1755,10 +1774,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759818</v>
+        <v>759658</v>
       </c>
       <c r="R11" t="n">
-        <v>7093876</v>
+        <v>7093955</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1818,10 +1837,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120116996</v>
+        <v>120117039</v>
       </c>
       <c r="B12" t="n">
-        <v>4766</v>
+        <v>78576</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,36 +1849,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100299</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1867,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759799</v>
+        <v>759732</v>
       </c>
       <c r="R12" t="n">
-        <v>7093877</v>
+        <v>7093922</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1930,10 +1943,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120117092</v>
+        <v>120116985</v>
       </c>
       <c r="B13" t="n">
-        <v>78576</v>
+        <v>4766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,30 +1955,36 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>100299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1973,10 +1992,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759688</v>
+        <v>759806</v>
       </c>
       <c r="R13" t="n">
-        <v>7093898</v>
+        <v>7093910</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2003,12 +2022,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2036,10 +2055,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120117228</v>
+        <v>120117194</v>
       </c>
       <c r="B14" t="n">
-        <v>57689</v>
+        <v>57336</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2048,20 +2067,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2072,7 +2091,11 @@
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2080,10 +2103,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759719</v>
+        <v>759658</v>
       </c>
       <c r="R14" t="n">
-        <v>7093964</v>
+        <v>7093955</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2142,10 +2165,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120116927</v>
+        <v>120117023</v>
       </c>
       <c r="B15" t="n">
-        <v>57689</v>
+        <v>78576</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2154,31 +2177,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2186,10 +2208,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>759991</v>
+        <v>759748</v>
       </c>
       <c r="R15" t="n">
-        <v>7093717</v>
+        <v>7094005</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2230,6 +2252,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2248,10 +2271,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120117194</v>
+        <v>120116927</v>
       </c>
       <c r="B16" t="n">
-        <v>57336</v>
+        <v>57689</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2260,20 +2283,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2284,11 +2307,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2296,10 +2315,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759658</v>
+        <v>759991</v>
       </c>
       <c r="R16" t="n">
-        <v>7093955</v>
+        <v>7093717</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2326,12 +2345,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2358,10 +2377,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120117023</v>
+        <v>120117228</v>
       </c>
       <c r="B17" t="n">
-        <v>78576</v>
+        <v>57689</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2370,30 +2389,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2401,10 +2421,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759748</v>
+        <v>759719</v>
       </c>
       <c r="R17" t="n">
-        <v>7094005</v>
+        <v>7093964</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2431,12 +2451,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2445,7 +2465,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2574,10 +2593,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120117422</v>
+        <v>120117695</v>
       </c>
       <c r="B19" t="n">
-        <v>57336</v>
+        <v>90545</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2586,35 +2605,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2622,10 +2636,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759709</v>
+        <v>759692</v>
       </c>
       <c r="R19" t="n">
-        <v>7094089</v>
+        <v>7094117</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2666,6 +2680,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2684,10 +2699,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120117729</v>
+        <v>120117299</v>
       </c>
       <c r="B20" t="n">
-        <v>5189</v>
+        <v>57473</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2696,36 +2711,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2733,10 +2743,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759692</v>
+        <v>759645</v>
       </c>
       <c r="R20" t="n">
-        <v>7094117</v>
+        <v>7094007</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2777,7 +2787,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2796,10 +2805,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120117216</v>
+        <v>120117092</v>
       </c>
       <c r="B21" t="n">
-        <v>57689</v>
+        <v>78576</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2808,31 +2817,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2840,10 +2848,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759669</v>
+        <v>759688</v>
       </c>
       <c r="R21" t="n">
-        <v>7093972</v>
+        <v>7093898</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2884,6 +2892,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2902,10 +2911,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120117039</v>
+        <v>120117422</v>
       </c>
       <c r="B22" t="n">
-        <v>78576</v>
+        <v>57336</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2918,26 +2927,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2945,10 +2959,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759732</v>
+        <v>759709</v>
       </c>
       <c r="R22" t="n">
-        <v>7093922</v>
+        <v>7094089</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2975,12 +2989,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2989,7 +3003,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3008,10 +3021,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120116948</v>
+        <v>120117216</v>
       </c>
       <c r="B23" t="n">
-        <v>8421</v>
+        <v>57689</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3024,32 +3037,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106554</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3057,10 +3065,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759991</v>
+        <v>759669</v>
       </c>
       <c r="R23" t="n">
-        <v>7093717</v>
+        <v>7093972</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3087,12 +3095,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3101,29 +3109,8 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3140,10 +3127,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120117695</v>
+        <v>120116996</v>
       </c>
       <c r="B24" t="n">
-        <v>90545</v>
+        <v>4766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3156,26 +3143,32 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>100299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3183,10 +3176,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759692</v>
+        <v>759799</v>
       </c>
       <c r="R24" t="n">
-        <v>7094117</v>
+        <v>7093877</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3213,12 +3206,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3246,10 +3239,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120117299</v>
+        <v>120117729</v>
       </c>
       <c r="B25" t="n">
-        <v>57473</v>
+        <v>5189</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3258,31 +3251,36 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>105930</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3290,10 +3288,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759645</v>
+        <v>759692</v>
       </c>
       <c r="R25" t="n">
-        <v>7094007</v>
+        <v>7094117</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3334,6 +3332,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3352,10 +3351,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120117175</v>
+        <v>120116961</v>
       </c>
       <c r="B26" t="n">
-        <v>90598</v>
+        <v>97847</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3364,30 +3363,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>219790</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3395,10 +3395,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759658</v>
+        <v>759818</v>
       </c>
       <c r="R26" t="n">
-        <v>7093955</v>
+        <v>7093876</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -1731,10 +1731,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120117175</v>
+        <v>120117228</v>
       </c>
       <c r="B11" t="n">
-        <v>90598</v>
+        <v>57689</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1743,30 +1743,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1774,10 +1775,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759658</v>
+        <v>759719</v>
       </c>
       <c r="R11" t="n">
-        <v>7093955</v>
+        <v>7093964</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1818,7 +1819,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1837,10 +1837,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120117039</v>
+        <v>120117216</v>
       </c>
       <c r="B12" t="n">
-        <v>78576</v>
+        <v>57689</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,30 +1849,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1880,10 +1881,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759732</v>
+        <v>759669</v>
       </c>
       <c r="R12" t="n">
-        <v>7093922</v>
+        <v>7093972</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1910,12 +1911,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1924,7 +1925,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1943,10 +1943,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120116985</v>
+        <v>120117092</v>
       </c>
       <c r="B13" t="n">
-        <v>4766</v>
+        <v>78576</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1955,36 +1955,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100299</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1992,10 +1986,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759806</v>
+        <v>759688</v>
       </c>
       <c r="R13" t="n">
-        <v>7093910</v>
+        <v>7093898</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2022,12 +2016,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2055,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120117194</v>
+        <v>120117695</v>
       </c>
       <c r="B14" t="n">
-        <v>57336</v>
+        <v>90545</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2067,35 +2061,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2103,10 +2092,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759658</v>
+        <v>759692</v>
       </c>
       <c r="R14" t="n">
-        <v>7093955</v>
+        <v>7094117</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2147,6 +2136,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2271,10 +2261,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120116927</v>
+        <v>120117321</v>
       </c>
       <c r="B16" t="n">
-        <v>57689</v>
+        <v>57336</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2283,20 +2273,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2307,7 +2297,11 @@
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2315,10 +2309,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759991</v>
+        <v>759730</v>
       </c>
       <c r="R16" t="n">
-        <v>7093717</v>
+        <v>7094006</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2345,12 +2339,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2377,10 +2371,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120117228</v>
+        <v>120117175</v>
       </c>
       <c r="B17" t="n">
-        <v>57689</v>
+        <v>90598</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2389,31 +2383,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2421,10 +2414,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759719</v>
+        <v>759658</v>
       </c>
       <c r="R17" t="n">
-        <v>7093964</v>
+        <v>7093955</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2465,6 +2458,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2483,7 +2477,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120117321</v>
+        <v>120117422</v>
       </c>
       <c r="B18" t="n">
         <v>57336</v>
@@ -2531,10 +2525,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759730</v>
+        <v>759709</v>
       </c>
       <c r="R18" t="n">
-        <v>7094006</v>
+        <v>7094089</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2593,10 +2587,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120117695</v>
+        <v>120117194</v>
       </c>
       <c r="B19" t="n">
-        <v>90545</v>
+        <v>57336</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2605,30 +2599,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2636,10 +2635,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759692</v>
+        <v>759658</v>
       </c>
       <c r="R19" t="n">
-        <v>7094117</v>
+        <v>7093955</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2680,7 +2679,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2805,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120117092</v>
+        <v>120117729</v>
       </c>
       <c r="B21" t="n">
-        <v>78576</v>
+        <v>5189</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2817,30 +2815,36 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>105930</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2848,10 +2852,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759688</v>
+        <v>759692</v>
       </c>
       <c r="R21" t="n">
-        <v>7093898</v>
+        <v>7094117</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2911,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120117422</v>
+        <v>120117039</v>
       </c>
       <c r="B22" t="n">
-        <v>57336</v>
+        <v>78576</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2927,31 +2931,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2959,10 +2958,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759709</v>
+        <v>759732</v>
       </c>
       <c r="R22" t="n">
-        <v>7094089</v>
+        <v>7093922</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2989,12 +2988,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3003,6 +3002,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120117216</v>
+        <v>120116961</v>
       </c>
       <c r="B23" t="n">
-        <v>57689</v>
+        <v>97847</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3037,27 +3037,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>219790</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3065,10 +3065,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759669</v>
+        <v>759818</v>
       </c>
       <c r="R23" t="n">
-        <v>7093972</v>
+        <v>7093876</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3109,6 +3109,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3239,10 +3240,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120117729</v>
+        <v>120116927</v>
       </c>
       <c r="B25" t="n">
-        <v>5189</v>
+        <v>57689</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3255,16 +3256,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3273,14 +3274,9 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3288,10 +3284,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759692</v>
+        <v>759991</v>
       </c>
       <c r="R25" t="n">
-        <v>7094117</v>
+        <v>7093717</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3318,12 +3314,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3332,7 +3328,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3351,10 +3346,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120116961</v>
+        <v>120116985</v>
       </c>
       <c r="B26" t="n">
-        <v>97847</v>
+        <v>4766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3367,27 +3362,32 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219790</v>
+        <v>100299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3395,10 +3395,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759818</v>
+        <v>759806</v>
       </c>
       <c r="R26" t="n">
-        <v>7093876</v>
+        <v>7093910</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3425,12 +3425,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -1599,10 +1599,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120116948</v>
+        <v>120116927</v>
       </c>
       <c r="B10" t="n">
-        <v>8421</v>
+        <v>57689</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,32 +1615,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1692,29 +1687,8 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1731,10 +1705,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120117228</v>
+        <v>120117194</v>
       </c>
       <c r="B11" t="n">
-        <v>57689</v>
+        <v>57336</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1743,20 +1717,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1767,7 +1741,11 @@
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1775,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759719</v>
+        <v>759658</v>
       </c>
       <c r="R11" t="n">
-        <v>7093964</v>
+        <v>7093955</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1837,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120117216</v>
+        <v>120117729</v>
       </c>
       <c r="B12" t="n">
-        <v>57689</v>
+        <v>5189</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1853,16 +1831,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1871,9 +1849,14 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1881,10 +1864,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759669</v>
+        <v>759692</v>
       </c>
       <c r="R12" t="n">
-        <v>7093972</v>
+        <v>7094117</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1925,6 +1908,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1943,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120117092</v>
+        <v>120117299</v>
       </c>
       <c r="B13" t="n">
-        <v>78576</v>
+        <v>57473</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1959,26 +1943,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1986,10 +1971,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759688</v>
+        <v>759645</v>
       </c>
       <c r="R13" t="n">
-        <v>7093898</v>
+        <v>7094007</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2030,7 +2015,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2049,10 +2033,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120117695</v>
+        <v>120117228</v>
       </c>
       <c r="B14" t="n">
-        <v>90545</v>
+        <v>57689</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2065,26 +2049,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2092,10 +2077,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759692</v>
+        <v>759719</v>
       </c>
       <c r="R14" t="n">
-        <v>7094117</v>
+        <v>7093964</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2136,7 +2121,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2155,7 +2139,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120117023</v>
+        <v>120117092</v>
       </c>
       <c r="B15" t="n">
         <v>78576</v>
@@ -2198,10 +2182,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>759748</v>
+        <v>759688</v>
       </c>
       <c r="R15" t="n">
-        <v>7094005</v>
+        <v>7093898</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2228,12 +2212,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2261,10 +2245,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120117321</v>
+        <v>120117695</v>
       </c>
       <c r="B16" t="n">
-        <v>57336</v>
+        <v>90545</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2273,35 +2257,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2309,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759730</v>
+        <v>759692</v>
       </c>
       <c r="R16" t="n">
-        <v>7094006</v>
+        <v>7094117</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2353,6 +2332,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2371,10 +2351,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120117175</v>
+        <v>120117422</v>
       </c>
       <c r="B17" t="n">
-        <v>90598</v>
+        <v>57336</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2387,26 +2367,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2414,10 +2399,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759658</v>
+        <v>759709</v>
       </c>
       <c r="R17" t="n">
-        <v>7093955</v>
+        <v>7094089</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2458,7 +2443,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2477,10 +2461,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120117422</v>
+        <v>120116948</v>
       </c>
       <c r="B18" t="n">
-        <v>57336</v>
+        <v>8421</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2489,33 +2473,34 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2525,10 +2510,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759709</v>
+        <v>759991</v>
       </c>
       <c r="R18" t="n">
-        <v>7094089</v>
+        <v>7093717</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2555,12 +2540,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2569,8 +2554,29 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2587,10 +2593,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120117194</v>
+        <v>120117175</v>
       </c>
       <c r="B19" t="n">
-        <v>57336</v>
+        <v>90598</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2603,31 +2609,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2679,6 +2680,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2697,10 +2699,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120117299</v>
+        <v>120117023</v>
       </c>
       <c r="B20" t="n">
-        <v>57473</v>
+        <v>78576</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2713,27 +2715,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2741,10 +2742,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759645</v>
+        <v>759748</v>
       </c>
       <c r="R20" t="n">
-        <v>7094007</v>
+        <v>7094005</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2771,12 +2772,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2785,6 +2786,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2803,10 +2805,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120117729</v>
+        <v>120117039</v>
       </c>
       <c r="B21" t="n">
-        <v>5189</v>
+        <v>78576</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2815,36 +2817,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>105930</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2852,10 +2848,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759692</v>
+        <v>759732</v>
       </c>
       <c r="R21" t="n">
-        <v>7094117</v>
+        <v>7093922</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2882,12 +2878,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,10 +2911,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120117039</v>
+        <v>120116961</v>
       </c>
       <c r="B22" t="n">
-        <v>78576</v>
+        <v>97847</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2927,30 +2923,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>219790</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2958,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759732</v>
+        <v>759818</v>
       </c>
       <c r="R22" t="n">
-        <v>7093922</v>
+        <v>7093876</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2988,12 +2985,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3021,10 +3018,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120116961</v>
+        <v>120117216</v>
       </c>
       <c r="B23" t="n">
-        <v>97847</v>
+        <v>57689</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3037,27 +3034,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219790</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3065,10 +3062,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759818</v>
+        <v>759669</v>
       </c>
       <c r="R23" t="n">
-        <v>7093876</v>
+        <v>7093972</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3109,7 +3106,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3128,10 +3124,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120116996</v>
+        <v>120117321</v>
       </c>
       <c r="B24" t="n">
-        <v>4766</v>
+        <v>57336</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3140,34 +3136,33 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3177,10 +3172,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759799</v>
+        <v>759730</v>
       </c>
       <c r="R24" t="n">
-        <v>7093877</v>
+        <v>7094006</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3207,12 +3202,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3221,7 +3216,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3240,10 +3234,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120116927</v>
+        <v>120116996</v>
       </c>
       <c r="B25" t="n">
-        <v>57689</v>
+        <v>4766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3256,27 +3250,32 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>100299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3284,10 +3283,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759991</v>
+        <v>759799</v>
       </c>
       <c r="R25" t="n">
-        <v>7093717</v>
+        <v>7093877</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3328,6 +3327,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -3461,7 +3461,7 @@
         <v>132181706</v>
       </c>
       <c r="B27" t="n">
-        <v>58320</v>
+        <v>58322</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
         <v>132191329</v>
       </c>
       <c r="B28" t="n">
-        <v>79347</v>
+        <v>79349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -3461,7 +3461,7 @@
         <v>132181706</v>
       </c>
       <c r="B27" t="n">
-        <v>58322</v>
+        <v>58323</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
         <v>132191329</v>
       </c>
       <c r="B28" t="n">
-        <v>79349</v>
+        <v>79351</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -3461,7 +3461,7 @@
         <v>132181706</v>
       </c>
       <c r="B27" t="n">
-        <v>58323</v>
+        <v>58327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
         <v>132191329</v>
       </c>
       <c r="B28" t="n">
-        <v>79351</v>
+        <v>79359</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -3461,7 +3461,7 @@
         <v>132181706</v>
       </c>
       <c r="B27" t="n">
-        <v>58327</v>
+        <v>58328</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
         <v>132191329</v>
       </c>
       <c r="B28" t="n">
-        <v>79359</v>
+        <v>79360</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -3568,7 +3568,7 @@
         <v>132191329</v>
       </c>
       <c r="B28" t="n">
-        <v>79360</v>
+        <v>79361</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115545071</v>
+        <v>115544914</v>
       </c>
       <c r="B2" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillklinten (Lillklinten), Vb</t>
+          <t>Långmyrkroken nästlav, Långmyrkroken nästlav, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>759586</v>
+        <v>759653</v>
       </c>
       <c r="R2" t="n">
-        <v>7094100</v>
+        <v>7093950</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -795,50 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115544900</v>
+        <v>115545406</v>
       </c>
       <c r="B3" t="n">
-        <v>78533</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6434</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långmyrkroken nästlav, Vb</t>
+          <t>Lillklinten, Lillklinten, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759653</v>
+        <v>759667</v>
       </c>
       <c r="R3" t="n">
-        <v>7093950</v>
+        <v>7094107</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -870,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115544914</v>
+        <v>115545462</v>
       </c>
       <c r="B4" t="n">
-        <v>78541</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,14 +920,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långmyrkroken nästlav (Långmyrkroken nästlav), Vb</t>
+          <t>Långmyrkroken capillaris, Långmyrkroken capillaris, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759653</v>
+        <v>759738</v>
       </c>
       <c r="R4" t="n">
-        <v>7093950</v>
+        <v>7094082</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -982,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,50 +996,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115545469</v>
+        <v>120117023</v>
       </c>
       <c r="B5" t="n">
-        <v>78699</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>230552</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långmyrkroken (Långmyrkroken), Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>759846</v>
+        <v>759748</v>
       </c>
       <c r="R5" t="n">
-        <v>7093780</v>
+        <v>7094005</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1089,57 +1064,43 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:19</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:19</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115545462</v>
+        <v>120117039</v>
       </c>
       <c r="B6" t="n">
-        <v>78541</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,16 +1126,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långmyrkroken capillaris (Långmyrkroken capillaris), Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>759738</v>
+        <v>759732</v>
       </c>
       <c r="R6" t="n">
-        <v>7094082</v>
+        <v>7093922</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1201,22 +1165,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:34</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:34</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,33 +1179,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115545405</v>
+        <v>120117092</v>
       </c>
       <c r="B7" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1259,34 +1209,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långmyrkroken capillaris (Långmyrkroken capillaris), Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>759670</v>
+        <v>759688</v>
       </c>
       <c r="R7" t="n">
-        <v>7094076</v>
+        <v>7093898</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1313,22 +1266,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,88 +1280,64 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115545470</v>
+        <v>132191329</v>
       </c>
       <c r="B8" t="n">
-        <v>78703</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79405</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1637</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cylinderskägglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Usnea cylindrica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Clerc</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långmyrkroken cylinder (Långmyrkroken), Vb</t>
+          <t>Violettgrå tagellav, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>759803</v>
+        <v>759683</v>
       </c>
       <c r="R8" t="n">
-        <v>7093963</v>
+        <v>7093922</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1445,29 +1364,29 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="b">
         <v>0</v>
@@ -1487,50 +1406,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115545471</v>
+        <v>115545405</v>
       </c>
       <c r="B9" t="n">
-        <v>78699</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>230552</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långmyrkroken bb (Långmyrkroken capillaris), Vb</t>
+          <t>Långmyrkroken capillaris, Långmyrkroken capillaris, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759724</v>
+        <v>759670</v>
       </c>
       <c r="R9" t="n">
-        <v>7094080</v>
+        <v>7094076</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1562,7 +1476,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,17 +1486,37 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1599,48 +1533,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120116996</v>
+        <v>120117569</v>
       </c>
       <c r="B10" t="n">
-        <v>4766</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1648,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759799</v>
+        <v>759659</v>
       </c>
       <c r="R10" t="n">
-        <v>7093877</v>
+        <v>7094103</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1678,12 +1601,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,54 +1634,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120117216</v>
+        <v>115545470</v>
       </c>
       <c r="B11" t="n">
-        <v>57689</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79518</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>1637</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Cylinderskägglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Usnea cylindrica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Clerc</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Långmyrkroken cylinder, Långmyrkroken, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759669</v>
+        <v>759803</v>
       </c>
       <c r="R11" t="n">
-        <v>7093972</v>
+        <v>7093963</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1785,19 +1699,29 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG11" t="b">
         <v>0</v>
@@ -1805,59 +1729,49 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120117422</v>
+        <v>120117695</v>
       </c>
       <c r="B12" t="n">
-        <v>57336</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1865,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759709</v>
+        <v>759692</v>
       </c>
       <c r="R12" t="n">
-        <v>7094089</v>
+        <v>7094117</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1909,6 +1823,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1927,53 +1842,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120117039</v>
+        <v>115544900</v>
       </c>
       <c r="B13" t="n">
-        <v>78576</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>6434</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Långmyrkroken nästlav, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759732</v>
+        <v>759653</v>
       </c>
       <c r="R13" t="n">
-        <v>7093922</v>
+        <v>7093950</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2000,12 +1907,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,34 +1931,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120117228</v>
+        <v>120117311</v>
       </c>
       <c r="B14" t="n">
-        <v>57689</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,27 +1960,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>6434</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2077,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759719</v>
+        <v>759623</v>
       </c>
       <c r="R14" t="n">
-        <v>7093964</v>
+        <v>7094019</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2121,6 +2031,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2142,16 +2053,11 @@
         <v>120117194</v>
       </c>
       <c r="B15" t="n">
-        <v>57336</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2249,15 +2155,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120116961</v>
+        <v>120117321</v>
       </c>
       <c r="B16" t="n">
-        <v>97847</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2265,27 +2166,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2293,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759818</v>
+        <v>759730</v>
       </c>
       <c r="R16" t="n">
-        <v>7093876</v>
+        <v>7094006</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2337,7 +2242,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2356,42 +2260,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120117092</v>
+        <v>120117422</v>
       </c>
       <c r="B17" t="n">
-        <v>78576</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2399,10 +2303,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759688</v>
+        <v>759709</v>
       </c>
       <c r="R17" t="n">
-        <v>7093898</v>
+        <v>7094089</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2443,7 +2347,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2462,15 +2365,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120117695</v>
+        <v>120117584</v>
       </c>
       <c r="B18" t="n">
-        <v>90545</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,26 +2376,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2505,10 +2408,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759692</v>
+        <v>759680</v>
       </c>
       <c r="R18" t="n">
-        <v>7094117</v>
+        <v>7094134</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2549,7 +2452,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2568,15 +2470,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120116927</v>
+        <v>115545071</v>
       </c>
       <c r="B19" t="n">
-        <v>57689</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2584,38 +2481,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Lillklinten, Lillklinten, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759991</v>
+        <v>759586</v>
       </c>
       <c r="R19" t="n">
-        <v>7093717</v>
+        <v>7094100</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2642,12 +2543,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2662,54 +2573,55 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120117175</v>
+        <v>120116985</v>
       </c>
       <c r="B20" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2717,10 +2629,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759658</v>
+        <v>759806</v>
       </c>
       <c r="R20" t="n">
-        <v>7093955</v>
+        <v>7093910</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2747,12 +2659,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2780,42 +2692,43 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120117023</v>
+        <v>120116996</v>
       </c>
       <c r="B21" t="n">
-        <v>78576</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>100299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2823,10 +2736,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759748</v>
+        <v>759799</v>
       </c>
       <c r="R21" t="n">
-        <v>7094005</v>
+        <v>7093877</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2886,32 +2799,27 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120117321</v>
+        <v>115581059</v>
       </c>
       <c r="B22" t="n">
-        <v>57336</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2920,24 +2828,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Lillklinten, Lillklinten, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759730</v>
+        <v>759635</v>
       </c>
       <c r="R22" t="n">
-        <v>7094006</v>
+        <v>7094098</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2964,12 +2864,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2984,27 +2894,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120117729</v>
+        <v>120116927</v>
       </c>
       <c r="B23" t="n">
-        <v>5189</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3012,16 +2917,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3030,14 +2935,9 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3045,10 +2945,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759692</v>
+        <v>759991</v>
       </c>
       <c r="R23" t="n">
-        <v>7094117</v>
+        <v>7093717</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3075,12 +2975,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3089,7 +2989,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3108,37 +3007,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120117299</v>
+        <v>120117216</v>
       </c>
       <c r="B24" t="n">
-        <v>57473</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3152,10 +3046,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759645</v>
+        <v>759669</v>
       </c>
       <c r="R24" t="n">
-        <v>7094007</v>
+        <v>7093972</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3214,15 +3108,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120116985</v>
+        <v>120117228</v>
       </c>
       <c r="B25" t="n">
-        <v>4766</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3230,32 +3119,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100299</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3263,10 +3147,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759806</v>
+        <v>759719</v>
       </c>
       <c r="R25" t="n">
-        <v>7093910</v>
+        <v>7093964</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3293,12 +3177,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3307,7 +3191,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3326,15 +3209,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120116948</v>
+        <v>132181706</v>
       </c>
       <c r="B26" t="n">
-        <v>8421</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3342,43 +3220,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106554</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Sista besöket, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759991</v>
+        <v>759781</v>
       </c>
       <c r="R26" t="n">
-        <v>7093717</v>
+        <v>7093970</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3405,12 +3274,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3419,84 +3298,67 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132181706</v>
+        <v>120116922</v>
       </c>
       <c r="B27" t="n">
-        <v>58328</v>
+        <v>58114</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sista besöket, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>759781</v>
+        <v>760031</v>
       </c>
       <c r="R27" t="n">
-        <v>7093970</v>
+        <v>7093709</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3523,22 +3385,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>16:03</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>16:03</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3553,22 +3405,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132191329</v>
+        <v>120117299</v>
       </c>
       <c r="B28" t="n">
-        <v>79361</v>
+        <v>58114</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3576,34 +3428,38 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>759683</v>
+        <v>759645</v>
       </c>
       <c r="R28" t="n">
-        <v>7093922</v>
+        <v>7094007</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3630,22 +3486,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3660,15 +3506,565 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120117729</v>
+      </c>
+      <c r="B29" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>759692</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7094117</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120116948</v>
+      </c>
+      <c r="B30" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>759991</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7093717</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120116961</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>759818</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7093876</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>115545469</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79515</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>230552</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Gropig skägglav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Usnea barbata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Långmyrkroken, Långmyrkroken, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>759846</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7093780</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
           <t>Isak Falk Eliasson</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
+      <c r="AX32" t="inlineStr">
         <is>
           <t>Isak Falk Eliasson</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr"/>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>115545471</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79515</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>230552</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Gropig skägglav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Usnea barbata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Långmyrkroken bb, Långmyrkroken capillaris, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>759724</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7094080</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115545462</v>
+        <v>135478612</v>
       </c>
       <c r="B4" t="n">
-        <v>79359</v>
+        <v>79405</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långmyrkroken capillaris, Långmyrkroken capillaris, Vb</t>
+          <t>Långmyrkroken, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -930,7 +930,7 @@
         <v>7094082</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,22 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1741,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120117695</v>
+        <v>135477718</v>
       </c>
       <c r="B12" t="n">
-        <v>91872</v>
+        <v>96410</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1752,40 +1752,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>2812</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759692</v>
+        <v>759797</v>
       </c>
       <c r="R12" t="n">
-        <v>7094117</v>
+        <v>7093887</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1809,12 +1806,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1823,29 +1830,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115544900</v>
+        <v>135477719</v>
       </c>
       <c r="B13" t="n">
-        <v>79351</v>
+        <v>96410</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1853,37 +1859,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6434</v>
+        <v>2812</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långmyrkroken nästlav, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759653</v>
+        <v>759767</v>
       </c>
       <c r="R13" t="n">
-        <v>7093950</v>
+        <v>7093964</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1907,22 +1913,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,10 +1955,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120117311</v>
+        <v>135477737</v>
       </c>
       <c r="B14" t="n">
-        <v>79351</v>
+        <v>92188</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1960,40 +1966,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6434</v>
+        <v>3008</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759623</v>
+        <v>759701</v>
       </c>
       <c r="R14" t="n">
-        <v>7094019</v>
+        <v>7094065</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2017,12 +2020,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>på liggande gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2031,75 +2049,66 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120117194</v>
+        <v>135477725</v>
       </c>
       <c r="B15" t="n">
-        <v>57950</v>
+        <v>89218</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>4412</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>759658</v>
+        <v>759743</v>
       </c>
       <c r="R15" t="n">
-        <v>7093955</v>
+        <v>7093897</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2123,12 +2132,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2143,22 +2162,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120117321</v>
+        <v>120117695</v>
       </c>
       <c r="B16" t="n">
-        <v>57950</v>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2166,31 +2185,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2198,10 +2212,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759730</v>
+        <v>759692</v>
       </c>
       <c r="R16" t="n">
-        <v>7094006</v>
+        <v>7094117</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2242,6 +2256,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2260,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120117422</v>
+        <v>115544900</v>
       </c>
       <c r="B17" t="n">
-        <v>57950</v>
+        <v>79351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2271,42 +2286,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Långmyrkroken nästlav, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759709</v>
+        <v>759653</v>
       </c>
       <c r="R17" t="n">
-        <v>7094089</v>
+        <v>7093950</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2333,12 +2340,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2353,22 +2370,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120117584</v>
+        <v>120117311</v>
       </c>
       <c r="B18" t="n">
-        <v>57950</v>
+        <v>79351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2376,31 +2393,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2408,10 +2420,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759680</v>
+        <v>759623</v>
       </c>
       <c r="R18" t="n">
-        <v>7094134</v>
+        <v>7094019</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2452,6 +2464,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2470,10 +2483,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115545071</v>
+        <v>135477739</v>
       </c>
       <c r="B19" t="n">
-        <v>57141</v>
+        <v>80499</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2481,45 +2494,40 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lillklinten, Lillklinten, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759586</v>
+        <v>759699</v>
       </c>
       <c r="R19" t="n">
-        <v>7094100</v>
+        <v>7094113</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2543,22 +2551,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2567,8 +2575,24 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2585,10 +2609,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120116985</v>
+        <v>120117194</v>
       </c>
       <c r="B20" t="n">
-        <v>4775</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2596,30 +2620,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2629,10 +2652,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759806</v>
+        <v>759658</v>
       </c>
       <c r="R20" t="n">
-        <v>7093910</v>
+        <v>7093955</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2659,12 +2682,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2673,7 +2696,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2692,10 +2714,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120116996</v>
+        <v>120117321</v>
       </c>
       <c r="B21" t="n">
-        <v>4775</v>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2703,30 +2725,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2736,10 +2757,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759799</v>
+        <v>759730</v>
       </c>
       <c r="R21" t="n">
-        <v>7093877</v>
+        <v>7094006</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2766,12 +2787,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2780,7 +2801,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2799,10 +2819,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115581059</v>
+        <v>120117422</v>
       </c>
       <c r="B22" t="n">
-        <v>58327</v>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2810,16 +2830,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2828,16 +2848,24 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lillklinten, Lillklinten, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759635</v>
+        <v>759709</v>
       </c>
       <c r="R22" t="n">
-        <v>7094098</v>
+        <v>7094089</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2864,22 +2892,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>16:27</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>16:27</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2894,22 +2912,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120116927</v>
+        <v>120117584</v>
       </c>
       <c r="B23" t="n">
-        <v>58327</v>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2917,16 +2935,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2937,7 +2955,11 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2945,10 +2967,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759991</v>
+        <v>759680</v>
       </c>
       <c r="R23" t="n">
-        <v>7093717</v>
+        <v>7094134</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2975,12 +2997,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3007,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120117216</v>
+        <v>115545071</v>
       </c>
       <c r="B24" t="n">
-        <v>58327</v>
+        <v>57141</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3018,38 +3040,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Lillklinten, Lillklinten, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759669</v>
+        <v>759586</v>
       </c>
       <c r="R24" t="n">
-        <v>7093972</v>
+        <v>7094100</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3076,12 +3102,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3096,22 +3132,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120117228</v>
+        <v>120116985</v>
       </c>
       <c r="B25" t="n">
-        <v>58327</v>
+        <v>4775</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3119,27 +3155,32 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>100299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3147,10 +3188,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759719</v>
+        <v>759806</v>
       </c>
       <c r="R25" t="n">
-        <v>7093964</v>
+        <v>7093910</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3177,12 +3218,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3191,6 +3232,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3209,10 +3251,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132181706</v>
+        <v>120116996</v>
       </c>
       <c r="B26" t="n">
-        <v>58349</v>
+        <v>4775</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3220,34 +3262,43 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>100299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sista besöket, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759781</v>
+        <v>759799</v>
       </c>
       <c r="R26" t="n">
-        <v>7093970</v>
+        <v>7093877</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3274,22 +3325,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:03</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:03</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3298,70 +3339,67 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120116922</v>
+        <v>135478598</v>
       </c>
       <c r="B27" t="n">
-        <v>58114</v>
+        <v>5181</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>760031</v>
+        <v>759797</v>
       </c>
       <c r="R27" t="n">
-        <v>7093709</v>
+        <v>7093900</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3385,12 +3423,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3401,65 +3449,76 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120117299</v>
+        <v>115581059</v>
       </c>
       <c r="B28" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Lillklinten, Lillklinten, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>759645</v>
+        <v>759635</v>
       </c>
       <c r="R28" t="n">
-        <v>7094007</v>
+        <v>7094098</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3486,12 +3545,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3506,22 +3575,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120117729</v>
+        <v>120116927</v>
       </c>
       <c r="B29" t="n">
-        <v>5199</v>
+        <v>58327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3529,16 +3598,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3547,14 +3616,9 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3562,10 +3626,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759692</v>
+        <v>759991</v>
       </c>
       <c r="R29" t="n">
-        <v>7094117</v>
+        <v>7093717</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3592,12 +3656,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3606,7 +3670,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3625,10 +3688,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120116948</v>
+        <v>120117216</v>
       </c>
       <c r="B30" t="n">
-        <v>8444</v>
+        <v>58327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3636,32 +3699,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106554</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3669,10 +3727,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>759991</v>
+        <v>759669</v>
       </c>
       <c r="R30" t="n">
-        <v>7093717</v>
+        <v>7093972</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3699,12 +3757,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3713,29 +3771,8 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3752,10 +3789,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120116961</v>
+        <v>120117228</v>
       </c>
       <c r="B31" t="n">
-        <v>99035</v>
+        <v>58327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3763,27 +3800,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219790</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3791,10 +3828,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>759818</v>
+        <v>759719</v>
       </c>
       <c r="R31" t="n">
-        <v>7093876</v>
+        <v>7093964</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3835,7 +3872,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3854,45 +3890,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>115545469</v>
+        <v>132181706</v>
       </c>
       <c r="B32" t="n">
-        <v>79515</v>
+        <v>58349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>230552</v>
+        <v>103015</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Långmyrkroken, Långmyrkroken, Vb</t>
+          <t>Sista besöket, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>759846</v>
+        <v>759781</v>
       </c>
       <c r="R32" t="n">
-        <v>7093780</v>
+        <v>7093970</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3919,29 +3955,29 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="b">
         <v>0</v>
@@ -3961,45 +3997,49 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>115545471</v>
+        <v>120116922</v>
       </c>
       <c r="B33" t="n">
-        <v>79515</v>
+        <v>58114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>230552</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Långmyrkroken bb, Långmyrkroken capillaris, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>759724</v>
+        <v>760031</v>
       </c>
       <c r="R33" t="n">
-        <v>7094080</v>
+        <v>7093709</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4026,29 +4066,19 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="b">
         <v>0</v>
@@ -4056,15 +4086,1415 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120117299</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>759645</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7094007</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135477724</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>759733</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7094018</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
           <t>Isak Falk Eliasson</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
+      <c r="AX35" t="inlineStr">
         <is>
           <t>Isak Falk Eliasson</t>
         </is>
       </c>
-      <c r="AY33" t="inlineStr"/>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135477727</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>759739</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7093883</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120117729</v>
+      </c>
+      <c r="B37" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>759692</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7094117</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120116948</v>
+      </c>
+      <c r="B38" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>759991</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7093717</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120116961</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>759818</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7093876</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135477716</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>759825</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7093924</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135477709</v>
+      </c>
+      <c r="B41" t="n">
+        <v>106199</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221154</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Skogsstjärna</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lysimachia europaea</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>759878</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7093775</v>
+      </c>
+      <c r="S41" t="n">
+        <v>12</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135477706</v>
+      </c>
+      <c r="B42" t="n">
+        <v>100806</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>760044</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7093709</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135477711</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>759843</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7093832</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135477712</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>759810</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7093860</v>
+      </c>
+      <c r="S44" t="n">
+        <v>6</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>115545469</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79515</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>230552</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Gropig skägglav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Usnea barbata</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Långmyrkroken, Långmyrkroken, Vb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>759846</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7093780</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>115545471</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79515</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>230552</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Gropig skägglav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Usnea barbata</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Långmyrkroken bb, Långmyrkroken capillaris, Vb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>759724</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7094080</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135478612</v>
+        <v>115545462</v>
       </c>
       <c r="B4" t="n">
-        <v>79405</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långmyrkroken, Vb</t>
+          <t>Långmyrkroken capillaris, Långmyrkroken capillaris, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -930,7 +930,7 @@
         <v>7094082</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,22 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1741,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135477718</v>
+        <v>120117695</v>
       </c>
       <c r="B12" t="n">
-        <v>96410</v>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1752,37 +1752,40 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2812</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>I20, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759797</v>
+        <v>759692</v>
       </c>
       <c r="R12" t="n">
-        <v>7093887</v>
+        <v>7094117</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1806,22 +1809,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1830,28 +1823,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135477719</v>
+        <v>115544900</v>
       </c>
       <c r="B13" t="n">
-        <v>96410</v>
+        <v>79351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,37 +1853,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2812</v>
+        <v>6434</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>I20, Vb</t>
+          <t>Långmyrkroken nästlav, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759767</v>
+        <v>759653</v>
       </c>
       <c r="R13" t="n">
-        <v>7093964</v>
+        <v>7093950</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1913,22 +1907,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1955,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135477737</v>
+        <v>120117311</v>
       </c>
       <c r="B14" t="n">
-        <v>92188</v>
+        <v>79351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1966,37 +1960,40 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3008</v>
+        <v>6434</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Timmerticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Amyloporia sinuosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Rajchenb. &amp; al.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>I20, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759701</v>
+        <v>759623</v>
       </c>
       <c r="R14" t="n">
-        <v>7094065</v>
+        <v>7094019</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2020,27 +2017,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>på liggande gran</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2049,66 +2031,75 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135477725</v>
+        <v>120117194</v>
       </c>
       <c r="B15" t="n">
-        <v>89218</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4412</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>I20, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>759743</v>
+        <v>759658</v>
       </c>
       <c r="R15" t="n">
-        <v>7093897</v>
+        <v>7093955</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2132,22 +2123,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2162,22 +2143,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120117695</v>
+        <v>120117321</v>
       </c>
       <c r="B16" t="n">
-        <v>91872</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2185,26 +2166,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2212,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759692</v>
+        <v>759730</v>
       </c>
       <c r="R16" t="n">
-        <v>7094117</v>
+        <v>7094006</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2256,7 +2242,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2275,10 +2260,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115544900</v>
+        <v>120117422</v>
       </c>
       <c r="B17" t="n">
-        <v>79351</v>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2286,34 +2271,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6434</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långmyrkroken nästlav, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759653</v>
+        <v>759709</v>
       </c>
       <c r="R17" t="n">
-        <v>7093950</v>
+        <v>7094089</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2340,22 +2333,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>17:05</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>17:05</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2370,22 +2353,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120117311</v>
+        <v>120117584</v>
       </c>
       <c r="B18" t="n">
-        <v>79351</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2393,26 +2376,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6434</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2420,10 +2408,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759623</v>
+        <v>759680</v>
       </c>
       <c r="R18" t="n">
-        <v>7094019</v>
+        <v>7094134</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2464,7 +2452,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2483,10 +2470,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135477739</v>
+        <v>115545071</v>
       </c>
       <c r="B19" t="n">
-        <v>80499</v>
+        <v>57141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2494,40 +2481,45 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6463</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>I20, Vb</t>
+          <t>Lillklinten, Lillklinten, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759699</v>
+        <v>759586</v>
       </c>
       <c r="R19" t="n">
-        <v>7094113</v>
+        <v>7094100</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2551,22 +2543,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2575,24 +2567,8 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2609,10 +2585,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120117194</v>
+        <v>120116985</v>
       </c>
       <c r="B20" t="n">
-        <v>57950</v>
+        <v>4775</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2620,29 +2596,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2652,10 +2629,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759658</v>
+        <v>759806</v>
       </c>
       <c r="R20" t="n">
-        <v>7093955</v>
+        <v>7093910</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2682,12 +2659,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2696,6 +2673,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2714,10 +2692,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120117321</v>
+        <v>120116996</v>
       </c>
       <c r="B21" t="n">
-        <v>57950</v>
+        <v>4775</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2725,29 +2703,30 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2757,10 +2736,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759730</v>
+        <v>759799</v>
       </c>
       <c r="R21" t="n">
-        <v>7094006</v>
+        <v>7093877</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2787,12 +2766,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2801,6 +2780,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2819,10 +2799,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120117422</v>
+        <v>115581059</v>
       </c>
       <c r="B22" t="n">
-        <v>57950</v>
+        <v>58327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2830,16 +2810,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2848,24 +2828,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Lillklinten, Lillklinten, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759709</v>
+        <v>759635</v>
       </c>
       <c r="R22" t="n">
-        <v>7094089</v>
+        <v>7094098</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2892,12 +2864,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,22 +2894,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120117584</v>
+        <v>120116927</v>
       </c>
       <c r="B23" t="n">
-        <v>57950</v>
+        <v>58327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2935,16 +2917,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2955,11 +2937,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2967,10 +2945,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759680</v>
+        <v>759991</v>
       </c>
       <c r="R23" t="n">
-        <v>7094134</v>
+        <v>7093717</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2997,12 +2975,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115545071</v>
+        <v>120117216</v>
       </c>
       <c r="B24" t="n">
-        <v>57141</v>
+        <v>58327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,42 +3018,38 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lillklinten, Lillklinten, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759586</v>
+        <v>759669</v>
       </c>
       <c r="R24" t="n">
-        <v>7094100</v>
+        <v>7093972</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3102,22 +3076,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>16:53</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>16:53</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3132,22 +3096,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120116985</v>
+        <v>120117228</v>
       </c>
       <c r="B25" t="n">
-        <v>4775</v>
+        <v>58327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3155,32 +3119,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100299</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3188,10 +3147,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759806</v>
+        <v>759719</v>
       </c>
       <c r="R25" t="n">
-        <v>7093910</v>
+        <v>7093964</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3218,12 +3177,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3232,7 +3191,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3251,10 +3209,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120116996</v>
+        <v>132181706</v>
       </c>
       <c r="B26" t="n">
-        <v>4775</v>
+        <v>58349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3262,43 +3220,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100299</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Sista besöket, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759799</v>
+        <v>759781</v>
       </c>
       <c r="R26" t="n">
-        <v>7093877</v>
+        <v>7093970</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3325,12 +3274,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3339,67 +3298,70 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135478598</v>
+        <v>120116922</v>
       </c>
       <c r="B27" t="n">
-        <v>5181</v>
+        <v>58114</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>I20, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>759797</v>
+        <v>760031</v>
       </c>
       <c r="R27" t="n">
-        <v>7093900</v>
+        <v>7093709</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3423,22 +3385,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:38</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:38</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3449,76 +3401,65 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115581059</v>
+        <v>120117299</v>
       </c>
       <c r="B28" t="n">
-        <v>58327</v>
+        <v>58114</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lillklinten, Lillklinten, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>759635</v>
+        <v>759645</v>
       </c>
       <c r="R28" t="n">
-        <v>7094098</v>
+        <v>7094007</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3545,22 +3486,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>16:27</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>16:27</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3575,22 +3506,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120116927</v>
+        <v>120117729</v>
       </c>
       <c r="B29" t="n">
-        <v>58327</v>
+        <v>5199</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3598,16 +3529,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103015</v>
+        <v>105930</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3616,9 +3547,14 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3626,10 +3562,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759991</v>
+        <v>759692</v>
       </c>
       <c r="R29" t="n">
-        <v>7093717</v>
+        <v>7094117</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3656,12 +3592,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3670,6 +3606,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3688,10 +3625,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120117216</v>
+        <v>120116948</v>
       </c>
       <c r="B30" t="n">
-        <v>58327</v>
+        <v>8444</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3699,27 +3636,32 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103015</v>
+        <v>106554</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3727,10 +3669,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>759669</v>
+        <v>759991</v>
       </c>
       <c r="R30" t="n">
-        <v>7093972</v>
+        <v>7093717</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3757,12 +3699,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3771,8 +3713,29 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3789,10 +3752,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120117228</v>
+        <v>120116961</v>
       </c>
       <c r="B31" t="n">
-        <v>58327</v>
+        <v>99035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3800,27 +3763,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>219790</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3828,10 +3791,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>759719</v>
+        <v>759818</v>
       </c>
       <c r="R31" t="n">
-        <v>7093964</v>
+        <v>7093876</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3872,6 +3835,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3890,45 +3854,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132181706</v>
+        <v>115545469</v>
       </c>
       <c r="B32" t="n">
-        <v>58349</v>
+        <v>79515</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
+        <v>230552</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sista besöket, Vb</t>
+          <t>Långmyrkroken, Långmyrkroken, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>759781</v>
+        <v>759846</v>
       </c>
       <c r="R32" t="n">
-        <v>7093970</v>
+        <v>7093780</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3955,29 +3919,29 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG32" t="b">
         <v>0</v>
@@ -3997,49 +3961,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120116922</v>
+        <v>115545471</v>
       </c>
       <c r="B33" t="n">
-        <v>58114</v>
+        <v>79515</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>230552</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Långmyrkroken bb, Långmyrkroken capillaris, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>760031</v>
+        <v>759724</v>
       </c>
       <c r="R33" t="n">
-        <v>7093709</v>
+        <v>7094080</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4066,19 +4026,29 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG33" t="b">
         <v>0</v>
@@ -4086,1415 +4056,15 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>120117299</v>
-      </c>
-      <c r="B34" t="n">
-        <v>58114</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Lillklinten, Umeå, Vb</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>759645</v>
-      </c>
-      <c r="R34" t="n">
-        <v>7094007</v>
-      </c>
-      <c r="S34" t="n">
-        <v>25</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>J-M Roberge</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>J-M Roberge</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>135477724</v>
-      </c>
-      <c r="B35" t="n">
-        <v>58136</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>I20, Vb</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>759733</v>
-      </c>
-      <c r="R35" t="n">
-        <v>7094018</v>
-      </c>
-      <c r="S35" t="n">
-        <v>10</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>135477727</v>
-      </c>
-      <c r="B36" t="n">
-        <v>58136</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>I20, Vb</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>759739</v>
-      </c>
-      <c r="R36" t="n">
-        <v>7093883</v>
-      </c>
-      <c r="S36" t="n">
-        <v>5</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>120117729</v>
-      </c>
-      <c r="B37" t="n">
-        <v>5199</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>105930</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Vågbandad barkbock</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Semanotus undatus</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Lillklinten, Umeå, Vb</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>759692</v>
-      </c>
-      <c r="R37" t="n">
-        <v>7094117</v>
-      </c>
-      <c r="S37" t="n">
-        <v>25</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="inlineStr"/>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>J-M Roberge</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>J-M Roberge</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>120116948</v>
-      </c>
-      <c r="B38" t="n">
-        <v>8444</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>106554</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Björksplintborre</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Scolytus ratzeburgii</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Lillklinten, Umeå, Vb</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>759991</v>
-      </c>
-      <c r="R38" t="n">
-        <v>7093717</v>
-      </c>
-      <c r="S38" t="n">
-        <v>25</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2024-09-02</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2024-09-02</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>J-M Roberge</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>J-M Roberge</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>120116961</v>
-      </c>
-      <c r="B39" t="n">
-        <v>99035</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>219790</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Dactylorhiza maculata</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Lillklinten, Umeå, Vb</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>759818</v>
-      </c>
-      <c r="R39" t="n">
-        <v>7093876</v>
-      </c>
-      <c r="S39" t="n">
-        <v>25</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="inlineStr"/>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>J-M Roberge</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>J-M Roberge</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>135477716</v>
-      </c>
-      <c r="B40" t="n">
-        <v>99112</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>219790</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Dactylorhiza maculata</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>I20, Vb</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>759825</v>
-      </c>
-      <c r="R40" t="n">
-        <v>7093924</v>
-      </c>
-      <c r="S40" t="n">
-        <v>5</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>135477709</v>
-      </c>
-      <c r="B41" t="n">
-        <v>106199</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>221154</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Skogsstjärna</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Lysimachia europaea</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(L.) U. Manns &amp; Anderb.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>I20, Vb</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>759878</v>
-      </c>
-      <c r="R41" t="n">
-        <v>7093775</v>
-      </c>
-      <c r="S41" t="n">
-        <v>12</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>135477706</v>
-      </c>
-      <c r="B42" t="n">
-        <v>100806</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>222584</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Bergsslok</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Melica nutans</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>I20, Vb</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>760044</v>
-      </c>
-      <c r="R42" t="n">
-        <v>7093709</v>
-      </c>
-      <c r="S42" t="n">
-        <v>5</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>135477711</v>
-      </c>
-      <c r="B43" t="n">
-        <v>99001</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>223049</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Ormbär</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Paris quadrifolia</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>I20, Vb</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>759843</v>
-      </c>
-      <c r="R43" t="n">
-        <v>7093832</v>
-      </c>
-      <c r="S43" t="n">
-        <v>5</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>135477712</v>
-      </c>
-      <c r="B44" t="n">
-        <v>98249</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>I20, Vb</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>759810</v>
-      </c>
-      <c r="R44" t="n">
-        <v>7093860</v>
-      </c>
-      <c r="S44" t="n">
-        <v>6</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>115545469</v>
-      </c>
-      <c r="B45" t="n">
-        <v>79515</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>230552</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Gropig skägglav</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Usnea barbata</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Långmyrkroken, Långmyrkroken, Vb</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>759846</v>
-      </c>
-      <c r="R45" t="n">
-        <v>7093780</v>
-      </c>
-      <c r="S45" t="n">
-        <v>25</v>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AD45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="b">
-        <v>1</v>
-      </c>
-      <c r="AG45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>115545471</v>
-      </c>
-      <c r="B46" t="n">
-        <v>79515</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>230552</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Gropig skägglav</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Usnea barbata</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Långmyrkroken bb, Långmyrkroken capillaris, Vb</t>
-        </is>
-      </c>
-      <c r="Q46" t="n">
-        <v>759724</v>
-      </c>
-      <c r="R46" t="n">
-        <v>7094080</v>
-      </c>
-      <c r="S46" t="n">
-        <v>25</v>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AD46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AG46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT46" t="inlineStr"/>
-      <c r="AW46" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115544914</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,13 +896,18 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115545406</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115545462</v>
+        <v>135478612</v>
       </c>
       <c r="B4" t="n">
-        <v>79359</v>
+        <v>79405</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,7 +935,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långmyrkroken capillaris, Långmyrkroken capillaris, Vb</t>
+          <t>Långmyrkroken, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -930,7 +945,7 @@
         <v>7094082</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,22 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135478612</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120117023</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120117039</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1296,6 +1326,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120117092</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1403,6 +1438,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132191329</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1530,6 +1570,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115545405</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1631,6 +1676,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120117569</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1738,13 +1788,18 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115545470</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120117695</v>
+        <v>135477718</v>
       </c>
       <c r="B12" t="n">
-        <v>91872</v>
+        <v>96410</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1752,40 +1807,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>2812</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759692</v>
+        <v>759797</v>
       </c>
       <c r="R12" t="n">
-        <v>7094117</v>
+        <v>7093887</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1809,12 +1861,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1823,29 +1885,33 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477718</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115544900</v>
+        <v>135477719</v>
       </c>
       <c r="B13" t="n">
-        <v>79351</v>
+        <v>96410</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1853,37 +1919,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6434</v>
+        <v>2812</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långmyrkroken nästlav, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759653</v>
+        <v>759767</v>
       </c>
       <c r="R13" t="n">
-        <v>7093950</v>
+        <v>7093964</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1907,22 +1973,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1946,13 +2012,18 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477719</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120117311</v>
+        <v>135477737</v>
       </c>
       <c r="B14" t="n">
-        <v>79351</v>
+        <v>92188</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1960,40 +2031,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6434</v>
+        <v>3008</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759623</v>
+        <v>759701</v>
       </c>
       <c r="R14" t="n">
-        <v>7094019</v>
+        <v>7094065</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2017,12 +2085,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>på liggande gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2031,75 +2114,71 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477737</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120117194</v>
+        <v>135477725</v>
       </c>
       <c r="B15" t="n">
-        <v>57950</v>
+        <v>89218</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>4412</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>759658</v>
+        <v>759743</v>
       </c>
       <c r="R15" t="n">
-        <v>7093955</v>
+        <v>7093897</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2123,12 +2202,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2143,22 +2232,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477725</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120117321</v>
+        <v>120117695</v>
       </c>
       <c r="B16" t="n">
-        <v>57950</v>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2166,31 +2260,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2198,10 +2287,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759730</v>
+        <v>759692</v>
       </c>
       <c r="R16" t="n">
-        <v>7094006</v>
+        <v>7094117</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2242,6 +2331,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2257,13 +2347,18 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120117695</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120117422</v>
+        <v>115544900</v>
       </c>
       <c r="B17" t="n">
-        <v>57950</v>
+        <v>79351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2271,42 +2366,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Långmyrkroken nästlav, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759709</v>
+        <v>759653</v>
       </c>
       <c r="R17" t="n">
-        <v>7094089</v>
+        <v>7093950</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2333,12 +2420,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2353,22 +2450,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115544900</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120117584</v>
+        <v>120117311</v>
       </c>
       <c r="B18" t="n">
-        <v>57950</v>
+        <v>79351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2376,31 +2478,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2408,10 +2505,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759680</v>
+        <v>759623</v>
       </c>
       <c r="R18" t="n">
-        <v>7094134</v>
+        <v>7094019</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2452,6 +2549,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2467,13 +2565,18 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120117311</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115545071</v>
+        <v>135477739</v>
       </c>
       <c r="B19" t="n">
-        <v>57141</v>
+        <v>80499</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2481,45 +2584,40 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lillklinten, Lillklinten, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759586</v>
+        <v>759699</v>
       </c>
       <c r="R19" t="n">
-        <v>7094100</v>
+        <v>7094113</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2543,22 +2641,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2567,8 +2665,24 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2582,13 +2696,18 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477739</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120116985</v>
+        <v>120117194</v>
       </c>
       <c r="B20" t="n">
-        <v>4775</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2596,30 +2715,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2629,10 +2747,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759806</v>
+        <v>759658</v>
       </c>
       <c r="R20" t="n">
-        <v>7093910</v>
+        <v>7093955</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2659,12 +2777,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2673,7 +2791,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2689,13 +2806,18 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120117194</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120116996</v>
+        <v>120117321</v>
       </c>
       <c r="B21" t="n">
-        <v>4775</v>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2703,30 +2825,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2736,10 +2857,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759799</v>
+        <v>759730</v>
       </c>
       <c r="R21" t="n">
-        <v>7093877</v>
+        <v>7094006</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2766,12 +2887,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2780,7 +2901,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2796,13 +2916,18 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120117321</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115581059</v>
+        <v>120117422</v>
       </c>
       <c r="B22" t="n">
-        <v>58327</v>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2810,16 +2935,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2828,16 +2953,24 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lillklinten, Lillklinten, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759635</v>
+        <v>759709</v>
       </c>
       <c r="R22" t="n">
-        <v>7094098</v>
+        <v>7094089</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2864,22 +2997,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>16:27</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>16:27</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2894,22 +3017,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120117422</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120116927</v>
+        <v>120117584</v>
       </c>
       <c r="B23" t="n">
-        <v>58327</v>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2917,16 +3045,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2937,7 +3065,11 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2945,10 +3077,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759991</v>
+        <v>759680</v>
       </c>
       <c r="R23" t="n">
-        <v>7093717</v>
+        <v>7094134</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2975,12 +3107,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3004,13 +3136,18 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120117584</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120117216</v>
+        <v>115545071</v>
       </c>
       <c r="B24" t="n">
-        <v>58327</v>
+        <v>57141</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3018,38 +3155,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Lillklinten, Lillklinten, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759669</v>
+        <v>759586</v>
       </c>
       <c r="R24" t="n">
-        <v>7093972</v>
+        <v>7094100</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3076,12 +3217,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3096,22 +3247,27 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115545071</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120117228</v>
+        <v>120116985</v>
       </c>
       <c r="B25" t="n">
-        <v>58327</v>
+        <v>4775</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3119,27 +3275,32 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>100299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3147,10 +3308,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759719</v>
+        <v>759806</v>
       </c>
       <c r="R25" t="n">
-        <v>7093964</v>
+        <v>7093910</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3177,12 +3338,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3191,6 +3352,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3206,13 +3368,18 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120116985</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132181706</v>
+        <v>120116996</v>
       </c>
       <c r="B26" t="n">
-        <v>58349</v>
+        <v>4775</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3220,34 +3387,43 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>100299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sista besöket, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759781</v>
+        <v>759799</v>
       </c>
       <c r="R26" t="n">
-        <v>7093970</v>
+        <v>7093877</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3274,22 +3450,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:03</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:03</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3298,70 +3464,72 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120116996</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120116922</v>
+        <v>135478598</v>
       </c>
       <c r="B27" t="n">
-        <v>58114</v>
+        <v>5181</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>760031</v>
+        <v>759797</v>
       </c>
       <c r="R27" t="n">
-        <v>7093709</v>
+        <v>7093900</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3385,12 +3553,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3401,65 +3579,81 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135478598</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120117299</v>
+        <v>115581059</v>
       </c>
       <c r="B28" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Lillklinten, Lillklinten, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>759645</v>
+        <v>759635</v>
       </c>
       <c r="R28" t="n">
-        <v>7094007</v>
+        <v>7094098</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3486,12 +3680,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3506,22 +3710,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115581059</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120117729</v>
+        <v>120116927</v>
       </c>
       <c r="B29" t="n">
-        <v>5199</v>
+        <v>58327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3529,16 +3738,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3547,14 +3756,9 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3562,10 +3766,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759692</v>
+        <v>759991</v>
       </c>
       <c r="R29" t="n">
-        <v>7094117</v>
+        <v>7093717</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3592,12 +3796,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3606,7 +3810,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3622,13 +3825,18 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120116927</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120116948</v>
+        <v>120117216</v>
       </c>
       <c r="B30" t="n">
-        <v>8444</v>
+        <v>58327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3636,32 +3844,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106554</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3669,10 +3872,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>759991</v>
+        <v>759669</v>
       </c>
       <c r="R30" t="n">
-        <v>7093717</v>
+        <v>7093972</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3699,12 +3902,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3713,29 +3916,8 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3749,13 +3931,18 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120117216</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120116961</v>
+        <v>120117228</v>
       </c>
       <c r="B31" t="n">
-        <v>99035</v>
+        <v>58327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3763,27 +3950,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219790</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3791,10 +3978,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>759818</v>
+        <v>759719</v>
       </c>
       <c r="R31" t="n">
-        <v>7093876</v>
+        <v>7093964</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3835,7 +4022,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3851,48 +4037,53 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120117228</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>115545469</v>
+        <v>132181706</v>
       </c>
       <c r="B32" t="n">
-        <v>79515</v>
+        <v>58349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>230552</v>
+        <v>103015</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Långmyrkroken, Långmyrkroken, Vb</t>
+          <t>Sista besöket, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>759846</v>
+        <v>759781</v>
       </c>
       <c r="R32" t="n">
-        <v>7093780</v>
+        <v>7093970</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3919,29 +4110,29 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="b">
         <v>0</v>
@@ -3958,48 +4149,57 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132181706</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>115545471</v>
+        <v>120116922</v>
       </c>
       <c r="B33" t="n">
-        <v>79515</v>
+        <v>58114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>230552</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Långmyrkroken bb, Långmyrkroken capillaris, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>759724</v>
+        <v>760031</v>
       </c>
       <c r="R33" t="n">
-        <v>7094080</v>
+        <v>7093709</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4026,29 +4226,19 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="b">
         <v>0</v>
@@ -4056,17 +4246,1534 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120116922</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120117299</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>759645</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7094007</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120117299</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135477724</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>759733</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7094018</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
           <t>Isak Falk Eliasson</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
+      <c r="AX35" t="inlineStr">
         <is>
           <t>Isak Falk Eliasson</t>
         </is>
       </c>
-      <c r="AY33" t="inlineStr"/>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477724</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135477727</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>759739</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7093883</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477727</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120117729</v>
+      </c>
+      <c r="B37" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>759692</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7094117</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120117729</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120116948</v>
+      </c>
+      <c r="B38" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>759991</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7093717</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120116948</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120116961</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>759818</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7093876</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120116961</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135477716</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>759825</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7093924</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477716</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135477709</v>
+      </c>
+      <c r="B41" t="n">
+        <v>106199</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221154</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Skogsstjärna</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lysimachia europaea</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>759878</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7093775</v>
+      </c>
+      <c r="S41" t="n">
+        <v>12</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477709</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135477706</v>
+      </c>
+      <c r="B42" t="n">
+        <v>100806</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>760044</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7093709</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477706</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135477711</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>759843</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7093832</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477711</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135477712</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>759810</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7093860</v>
+      </c>
+      <c r="S44" t="n">
+        <v>6</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477712</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>115545469</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79515</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>230552</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Gropig skägglav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Usnea barbata</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Långmyrkroken, Långmyrkroken, Vb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>759846</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7093780</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115545469</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>115545471</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79515</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>230552</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Gropig skägglav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Usnea barbata</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Långmyrkroken bb, Långmyrkroken capillaris, Vb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>759724</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7094080</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115545471</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>135478612</v>
       </c>
       <c r="B4" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>135477718</v>
       </c>
       <c r="B12" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>135477719</v>
       </c>
       <c r="B13" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>135477737</v>
       </c>
       <c r="B14" t="n">
-        <v>92188</v>
+        <v>92230</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>135477725</v>
       </c>
       <c r="B15" t="n">
-        <v>89218</v>
+        <v>89260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>135477739</v>
       </c>
       <c r="B19" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>135477724</v>
       </c>
       <c r="B35" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>135477727</v>
       </c>
       <c r="B36" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>135477716</v>
       </c>
       <c r="B40" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>135477709</v>
       </c>
       <c r="B41" t="n">
-        <v>106199</v>
+        <v>106254</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>135477706</v>
       </c>
       <c r="B42" t="n">
-        <v>100806</v>
+        <v>100854</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>135477711</v>
       </c>
       <c r="B43" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>135477712</v>
       </c>
       <c r="B44" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>135478612</v>
       </c>
       <c r="B4" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>135477718</v>
       </c>
       <c r="B12" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>135477719</v>
       </c>
       <c r="B13" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>135477737</v>
       </c>
       <c r="B14" t="n">
-        <v>92230</v>
+        <v>92257</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>135477725</v>
       </c>
       <c r="B15" t="n">
-        <v>89260</v>
+        <v>89287</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>135477739</v>
       </c>
       <c r="B19" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>135477716</v>
       </c>
       <c r="B40" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>135477709</v>
       </c>
       <c r="B41" t="n">
-        <v>106254</v>
+        <v>106281</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>135477706</v>
       </c>
       <c r="B42" t="n">
-        <v>100854</v>
+        <v>100881</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>135477711</v>
       </c>
       <c r="B43" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>135477712</v>
       </c>
       <c r="B44" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ33"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115545462</v>
+        <v>135478612</v>
       </c>
       <c r="B4" t="n">
-        <v>79359</v>
+        <v>79473</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långmyrkroken capillaris, Långmyrkroken capillaris, Vb</t>
+          <t>Långmyrkroken, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -945,7 +945,7 @@
         <v>7094082</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,7 +1010,7 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115545462</t>
+          <t>https://artportalen.se/Sighting/135478612</t>
         </is>
       </c>
     </row>
@@ -1796,10 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120117695</v>
+        <v>135477718</v>
       </c>
       <c r="B12" t="n">
-        <v>91872</v>
+        <v>96486</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1807,40 +1807,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>2812</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759692</v>
+        <v>759797</v>
       </c>
       <c r="R12" t="n">
-        <v>7094117</v>
+        <v>7093887</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1864,12 +1861,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1878,34 +1885,33 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117695</t>
+          <t>https://artportalen.se/Sighting/135477718</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115544900</v>
+        <v>135477719</v>
       </c>
       <c r="B13" t="n">
-        <v>79351</v>
+        <v>96486</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,37 +1919,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6434</v>
+        <v>2812</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långmyrkroken nästlav, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759653</v>
+        <v>759767</v>
       </c>
       <c r="R13" t="n">
-        <v>7093950</v>
+        <v>7093964</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1967,22 +1973,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2008,16 +2014,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115544900</t>
+          <t>https://artportalen.se/Sighting/135477719</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120117311</v>
+        <v>135477737</v>
       </c>
       <c r="B14" t="n">
-        <v>79351</v>
+        <v>92262</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2025,40 +2031,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6434</v>
+        <v>3008</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759623</v>
+        <v>759701</v>
       </c>
       <c r="R14" t="n">
-        <v>7094019</v>
+        <v>7094065</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2082,12 +2085,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>på liggande gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2096,80 +2114,71 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117311</t>
+          <t>https://artportalen.se/Sighting/135477737</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120117194</v>
+        <v>135477725</v>
       </c>
       <c r="B15" t="n">
-        <v>57950</v>
+        <v>89290</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>4412</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>759658</v>
+        <v>759743</v>
       </c>
       <c r="R15" t="n">
-        <v>7093955</v>
+        <v>7093897</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2193,12 +2202,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2213,27 +2232,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117194</t>
+          <t>https://artportalen.se/Sighting/135477725</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120117321</v>
+        <v>120117695</v>
       </c>
       <c r="B16" t="n">
-        <v>57950</v>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2241,31 +2260,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2273,10 +2287,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759730</v>
+        <v>759692</v>
       </c>
       <c r="R16" t="n">
-        <v>7094006</v>
+        <v>7094117</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2317,6 +2331,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2334,16 +2349,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117321</t>
+          <t>https://artportalen.se/Sighting/120117695</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120117422</v>
+        <v>115544900</v>
       </c>
       <c r="B17" t="n">
-        <v>57950</v>
+        <v>79351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2351,42 +2366,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Långmyrkroken nästlav, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759709</v>
+        <v>759653</v>
       </c>
       <c r="R17" t="n">
-        <v>7094089</v>
+        <v>7093950</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2413,12 +2420,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2433,27 +2450,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117422</t>
+          <t>https://artportalen.se/Sighting/115544900</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120117584</v>
+        <v>120117311</v>
       </c>
       <c r="B18" t="n">
-        <v>57950</v>
+        <v>79351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2461,31 +2478,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2493,10 +2505,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759680</v>
+        <v>759623</v>
       </c>
       <c r="R18" t="n">
-        <v>7094134</v>
+        <v>7094019</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2537,6 +2549,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2554,16 +2567,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117584</t>
+          <t>https://artportalen.se/Sighting/120117311</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115545071</v>
+        <v>135477739</v>
       </c>
       <c r="B19" t="n">
-        <v>57141</v>
+        <v>80567</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2571,45 +2584,40 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lillklinten, Lillklinten, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759586</v>
+        <v>759699</v>
       </c>
       <c r="R19" t="n">
-        <v>7094100</v>
+        <v>7094113</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2633,22 +2641,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2657,8 +2665,24 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2674,16 +2698,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115545071</t>
+          <t>https://artportalen.se/Sighting/135477739</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120116985</v>
+        <v>120117194</v>
       </c>
       <c r="B20" t="n">
-        <v>4775</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2691,30 +2715,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2724,10 +2747,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759806</v>
+        <v>759658</v>
       </c>
       <c r="R20" t="n">
-        <v>7093910</v>
+        <v>7093955</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2754,12 +2777,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2768,7 +2791,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2786,16 +2808,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116985</t>
+          <t>https://artportalen.se/Sighting/120117194</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120116996</v>
+        <v>120117321</v>
       </c>
       <c r="B21" t="n">
-        <v>4775</v>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,30 +2825,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2836,10 +2857,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759799</v>
+        <v>759730</v>
       </c>
       <c r="R21" t="n">
-        <v>7093877</v>
+        <v>7094006</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2866,12 +2887,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2880,7 +2901,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2898,16 +2918,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116996</t>
+          <t>https://artportalen.se/Sighting/120117321</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115581059</v>
+        <v>120117422</v>
       </c>
       <c r="B22" t="n">
-        <v>58327</v>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,16 +2935,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2933,16 +2953,24 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lillklinten, Lillklinten, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759635</v>
+        <v>759709</v>
       </c>
       <c r="R22" t="n">
-        <v>7094098</v>
+        <v>7094089</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2969,22 +2997,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>16:27</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>16:27</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2999,27 +3017,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115581059</t>
+          <t>https://artportalen.se/Sighting/120117422</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120116927</v>
+        <v>120117584</v>
       </c>
       <c r="B23" t="n">
-        <v>58327</v>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3027,16 +3045,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3047,7 +3065,11 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3055,10 +3077,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759991</v>
+        <v>759680</v>
       </c>
       <c r="R23" t="n">
-        <v>7093717</v>
+        <v>7094134</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3085,12 +3107,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3116,16 +3138,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116927</t>
+          <t>https://artportalen.se/Sighting/120117584</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120117216</v>
+        <v>115545071</v>
       </c>
       <c r="B24" t="n">
-        <v>58327</v>
+        <v>57141</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3133,38 +3155,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Lillklinten, Lillklinten, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759669</v>
+        <v>759586</v>
       </c>
       <c r="R24" t="n">
-        <v>7093972</v>
+        <v>7094100</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3191,12 +3217,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3211,27 +3247,27 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117216</t>
+          <t>https://artportalen.se/Sighting/115545071</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120117228</v>
+        <v>120116985</v>
       </c>
       <c r="B25" t="n">
-        <v>58327</v>
+        <v>4775</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3239,27 +3275,32 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>100299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3267,10 +3308,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759719</v>
+        <v>759806</v>
       </c>
       <c r="R25" t="n">
-        <v>7093964</v>
+        <v>7093910</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3297,12 +3338,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3311,6 +3352,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3328,16 +3370,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117228</t>
+          <t>https://artportalen.se/Sighting/120116985</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132181706</v>
+        <v>120116996</v>
       </c>
       <c r="B26" t="n">
-        <v>58349</v>
+        <v>4775</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3345,34 +3387,43 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>100299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sista besöket, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759781</v>
+        <v>759799</v>
       </c>
       <c r="R26" t="n">
-        <v>7093970</v>
+        <v>7093877</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3399,22 +3450,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:03</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:03</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3423,75 +3464,72 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132181706</t>
+          <t>https://artportalen.se/Sighting/120116996</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120116922</v>
+        <v>135478598</v>
       </c>
       <c r="B27" t="n">
-        <v>58114</v>
+        <v>5181</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>760031</v>
+        <v>759797</v>
       </c>
       <c r="R27" t="n">
-        <v>7093709</v>
+        <v>7093900</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3515,12 +3553,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3531,70 +3579,81 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116922</t>
+          <t>https://artportalen.se/Sighting/135478598</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120117299</v>
+        <v>115581059</v>
       </c>
       <c r="B28" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Lillklinten, Lillklinten, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>759645</v>
+        <v>759635</v>
       </c>
       <c r="R28" t="n">
-        <v>7094007</v>
+        <v>7094098</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3621,12 +3680,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3641,27 +3710,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117299</t>
+          <t>https://artportalen.se/Sighting/115581059</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120117729</v>
+        <v>120116927</v>
       </c>
       <c r="B29" t="n">
-        <v>5199</v>
+        <v>58327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3669,16 +3738,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3687,14 +3756,9 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3702,10 +3766,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759692</v>
+        <v>759991</v>
       </c>
       <c r="R29" t="n">
-        <v>7094117</v>
+        <v>7093717</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3732,12 +3796,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3746,7 +3810,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3764,16 +3827,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117729</t>
+          <t>https://artportalen.se/Sighting/120116927</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120116948</v>
+        <v>120117216</v>
       </c>
       <c r="B30" t="n">
-        <v>8444</v>
+        <v>58327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3781,32 +3844,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106554</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3814,10 +3872,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>759991</v>
+        <v>759669</v>
       </c>
       <c r="R30" t="n">
-        <v>7093717</v>
+        <v>7093972</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3844,12 +3902,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3858,29 +3916,8 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3896,16 +3933,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116948</t>
+          <t>https://artportalen.se/Sighting/120117216</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120116961</v>
+        <v>120117228</v>
       </c>
       <c r="B31" t="n">
-        <v>99035</v>
+        <v>58327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3913,27 +3950,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219790</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3941,10 +3978,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>759818</v>
+        <v>759719</v>
       </c>
       <c r="R31" t="n">
-        <v>7093876</v>
+        <v>7093964</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3985,7 +4022,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4003,51 +4039,51 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116961</t>
+          <t>https://artportalen.se/Sighting/120117228</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>115545469</v>
+        <v>132181706</v>
       </c>
       <c r="B32" t="n">
-        <v>79515</v>
+        <v>58349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>230552</v>
+        <v>103015</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Långmyrkroken, Långmyrkroken, Vb</t>
+          <t>Sista besöket, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>759846</v>
+        <v>759781</v>
       </c>
       <c r="R32" t="n">
-        <v>7093780</v>
+        <v>7093970</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4074,29 +4110,29 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="b">
         <v>0</v>
@@ -4115,51 +4151,55 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115545469</t>
+          <t>https://artportalen.se/Sighting/132181706</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>115545471</v>
+        <v>120116922</v>
       </c>
       <c r="B33" t="n">
-        <v>79515</v>
+        <v>58114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>230552</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Långmyrkroken bb, Långmyrkroken capillaris, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>759724</v>
+        <v>760031</v>
       </c>
       <c r="R33" t="n">
-        <v>7094080</v>
+        <v>7093709</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4186,29 +4226,19 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="b">
         <v>0</v>
@@ -4216,16 +4246,1583 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120116922</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120117299</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>759645</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7094007</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120117299</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135477724</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>759733</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7094018</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477724</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135477727</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>759739</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7093883</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477727</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120117729</v>
+      </c>
+      <c r="B37" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>759692</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7094117</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120117729</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120116948</v>
+      </c>
+      <c r="B38" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>759991</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7093717</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120116948</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120116961</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>759818</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7093876</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120116961</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135477716</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99191</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>759825</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7093924</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477716</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135477709</v>
+      </c>
+      <c r="B41" t="n">
+        <v>106286</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221154</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Skogsstjärna</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lysimachia europaea</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>759878</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7093775</v>
+      </c>
+      <c r="S41" t="n">
+        <v>12</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477709</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135866265</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99932</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222306</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Stjärnstarr</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Carex echinata</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Murray</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Östra skjultfältsvägen, Östra skjultfältsvägen, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>759839</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7093779</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Tomas Sandström</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Tomas Sandström</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135866265</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135477706</v>
+      </c>
+      <c r="B43" t="n">
+        <v>100886</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>760044</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7093709</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477706</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135477711</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99080</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>759843</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7093832</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477711</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135477712</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98325</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>759810</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7093860</v>
+      </c>
+      <c r="S45" t="n">
+        <v>6</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477712</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>115545469</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79515</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>230552</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Gropig skägglav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Usnea barbata</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Långmyrkroken, Långmyrkroken, Vb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>759846</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7093780</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115545469</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>115545471</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79515</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>230552</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Gropig skägglav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Usnea barbata</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Långmyrkroken bb, Långmyrkroken capillaris, Vb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>759724</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7094080</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/115545471</t>
         </is>
@@ -4265,6 +5862,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -1799,7 +1799,7 @@
         <v>135477718</v>
       </c>
       <c r="B12" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>135477719</v>
       </c>
       <c r="B13" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>135477737</v>
       </c>
       <c r="B14" t="n">
-        <v>92262</v>
+        <v>92264</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>135477725</v>
       </c>
       <c r="B15" t="n">
-        <v>89290</v>
+        <v>89292</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>135477716</v>
       </c>
       <c r="B40" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>135477709</v>
       </c>
       <c r="B41" t="n">
-        <v>106286</v>
+        <v>106288</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>135866265</v>
       </c>
       <c r="B42" t="n">
-        <v>99932</v>
+        <v>99934</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>135477706</v>
       </c>
       <c r="B43" t="n">
-        <v>100886</v>
+        <v>100888</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>135477711</v>
       </c>
       <c r="B44" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>135477712</v>
       </c>
       <c r="B45" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ47"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135478612</v>
+        <v>115545462</v>
       </c>
       <c r="B4" t="n">
-        <v>79473</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långmyrkroken, Vb</t>
+          <t>Långmyrkroken capillaris, Långmyrkroken capillaris, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -945,7 +945,7 @@
         <v>7094082</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,7 +1010,7 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135478612</t>
+          <t>https://artportalen.se/Sighting/115545462</t>
         </is>
       </c>
     </row>
@@ -1796,10 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135477718</v>
+        <v>120117695</v>
       </c>
       <c r="B12" t="n">
-        <v>96488</v>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1807,37 +1807,40 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2812</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>I20, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759797</v>
+        <v>759692</v>
       </c>
       <c r="R12" t="n">
-        <v>7093887</v>
+        <v>7094117</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1861,22 +1864,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1885,33 +1878,34 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477718</t>
+          <t>https://artportalen.se/Sighting/120117695</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135477719</v>
+        <v>115544900</v>
       </c>
       <c r="B13" t="n">
-        <v>96488</v>
+        <v>79351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1919,37 +1913,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2812</v>
+        <v>6434</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>I20, Vb</t>
+          <t>Långmyrkroken nästlav, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759767</v>
+        <v>759653</v>
       </c>
       <c r="R13" t="n">
-        <v>7093964</v>
+        <v>7093950</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1973,22 +1967,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,16 +2008,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477719</t>
+          <t>https://artportalen.se/Sighting/115544900</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135477737</v>
+        <v>120117311</v>
       </c>
       <c r="B14" t="n">
-        <v>92264</v>
+        <v>79351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2031,37 +2025,40 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3008</v>
+        <v>6434</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Timmerticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Amyloporia sinuosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Rajchenb. &amp; al.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>I20, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759701</v>
+        <v>759623</v>
       </c>
       <c r="R14" t="n">
-        <v>7094065</v>
+        <v>7094019</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2085,27 +2082,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>på liggande gran</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2114,71 +2096,80 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477737</t>
+          <t>https://artportalen.se/Sighting/120117311</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135477725</v>
+        <v>120117194</v>
       </c>
       <c r="B15" t="n">
-        <v>89292</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4412</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>I20, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>759743</v>
+        <v>759658</v>
       </c>
       <c r="R15" t="n">
-        <v>7093897</v>
+        <v>7093955</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2202,22 +2193,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2232,27 +2213,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477725</t>
+          <t>https://artportalen.se/Sighting/120117194</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120117695</v>
+        <v>120117321</v>
       </c>
       <c r="B16" t="n">
-        <v>91872</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2260,26 +2241,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2287,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759692</v>
+        <v>759730</v>
       </c>
       <c r="R16" t="n">
-        <v>7094117</v>
+        <v>7094006</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2331,7 +2317,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2349,16 +2334,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117695</t>
+          <t>https://artportalen.se/Sighting/120117321</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115544900</v>
+        <v>120117422</v>
       </c>
       <c r="B17" t="n">
-        <v>79351</v>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,34 +2351,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6434</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långmyrkroken nästlav, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759653</v>
+        <v>759709</v>
       </c>
       <c r="R17" t="n">
-        <v>7093950</v>
+        <v>7094089</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2420,22 +2413,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>17:05</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>17:05</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2450,27 +2433,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115544900</t>
+          <t>https://artportalen.se/Sighting/120117422</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120117311</v>
+        <v>120117584</v>
       </c>
       <c r="B18" t="n">
-        <v>79351</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,26 +2461,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6434</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2505,10 +2493,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759623</v>
+        <v>759680</v>
       </c>
       <c r="R18" t="n">
-        <v>7094019</v>
+        <v>7094134</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2549,7 +2537,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2567,16 +2554,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117311</t>
+          <t>https://artportalen.se/Sighting/120117584</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135477739</v>
+        <v>115545071</v>
       </c>
       <c r="B19" t="n">
-        <v>80567</v>
+        <v>57141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2584,40 +2571,45 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6463</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>I20, Vb</t>
+          <t>Lillklinten, Lillklinten, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759699</v>
+        <v>759586</v>
       </c>
       <c r="R19" t="n">
-        <v>7094113</v>
+        <v>7094100</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2641,22 +2633,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2665,24 +2657,8 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2698,16 +2674,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477739</t>
+          <t>https://artportalen.se/Sighting/115545071</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120117194</v>
+        <v>120116985</v>
       </c>
       <c r="B20" t="n">
-        <v>57950</v>
+        <v>4775</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,29 +2691,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2747,10 +2724,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759658</v>
+        <v>759806</v>
       </c>
       <c r="R20" t="n">
-        <v>7093955</v>
+        <v>7093910</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2777,12 +2754,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2791,6 +2768,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2808,16 +2786,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117194</t>
+          <t>https://artportalen.se/Sighting/120116985</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120117321</v>
+        <v>120116996</v>
       </c>
       <c r="B21" t="n">
-        <v>57950</v>
+        <v>4775</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2825,29 +2803,30 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2857,10 +2836,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759730</v>
+        <v>759799</v>
       </c>
       <c r="R21" t="n">
-        <v>7094006</v>
+        <v>7093877</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2887,12 +2866,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2901,6 +2880,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2918,16 +2898,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117321</t>
+          <t>https://artportalen.se/Sighting/120116996</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120117422</v>
+        <v>115581059</v>
       </c>
       <c r="B22" t="n">
-        <v>57950</v>
+        <v>58327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2935,16 +2915,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2953,24 +2933,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Lillklinten, Lillklinten, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759709</v>
+        <v>759635</v>
       </c>
       <c r="R22" t="n">
-        <v>7094089</v>
+        <v>7094098</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2997,12 +2969,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3017,27 +2999,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117422</t>
+          <t>https://artportalen.se/Sighting/115581059</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120117584</v>
+        <v>120116927</v>
       </c>
       <c r="B23" t="n">
-        <v>57950</v>
+        <v>58327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3045,16 +3027,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3065,11 +3047,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3077,10 +3055,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759680</v>
+        <v>759991</v>
       </c>
       <c r="R23" t="n">
-        <v>7094134</v>
+        <v>7093717</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3107,12 +3085,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3138,16 +3116,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117584</t>
+          <t>https://artportalen.se/Sighting/120116927</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115545071</v>
+        <v>120117216</v>
       </c>
       <c r="B24" t="n">
-        <v>57141</v>
+        <v>58327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3155,42 +3133,38 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lillklinten, Lillklinten, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759586</v>
+        <v>759669</v>
       </c>
       <c r="R24" t="n">
-        <v>7094100</v>
+        <v>7093972</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3217,22 +3191,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>16:53</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>16:53</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3247,27 +3211,27 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115545071</t>
+          <t>https://artportalen.se/Sighting/120117216</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120116985</v>
+        <v>120117228</v>
       </c>
       <c r="B25" t="n">
-        <v>4775</v>
+        <v>58327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3275,32 +3239,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100299</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3308,10 +3267,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759806</v>
+        <v>759719</v>
       </c>
       <c r="R25" t="n">
-        <v>7093910</v>
+        <v>7093964</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3338,12 +3297,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3352,7 +3311,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3370,16 +3328,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116985</t>
+          <t>https://artportalen.se/Sighting/120117228</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120116996</v>
+        <v>132181706</v>
       </c>
       <c r="B26" t="n">
-        <v>4775</v>
+        <v>58349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3387,43 +3345,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100299</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Sista besöket, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759799</v>
+        <v>759781</v>
       </c>
       <c r="R26" t="n">
-        <v>7093877</v>
+        <v>7093970</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3450,12 +3399,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3464,72 +3423,75 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116996</t>
+          <t>https://artportalen.se/Sighting/132181706</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135478598</v>
+        <v>120116922</v>
       </c>
       <c r="B27" t="n">
-        <v>5181</v>
+        <v>58114</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>I20, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>759797</v>
+        <v>760031</v>
       </c>
       <c r="R27" t="n">
-        <v>7093900</v>
+        <v>7093709</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3553,22 +3515,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:38</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:38</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3579,81 +3531,70 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135478598</t>
+          <t>https://artportalen.se/Sighting/120116922</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115581059</v>
+        <v>120117299</v>
       </c>
       <c r="B28" t="n">
-        <v>58327</v>
+        <v>58114</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lillklinten, Lillklinten, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>759635</v>
+        <v>759645</v>
       </c>
       <c r="R28" t="n">
-        <v>7094098</v>
+        <v>7094007</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3680,22 +3621,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>16:27</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>16:27</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3710,27 +3641,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115581059</t>
+          <t>https://artportalen.se/Sighting/120117299</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120116927</v>
+        <v>120117729</v>
       </c>
       <c r="B29" t="n">
-        <v>58327</v>
+        <v>5199</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3738,16 +3669,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103015</v>
+        <v>105930</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3756,9 +3687,14 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3766,10 +3702,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759991</v>
+        <v>759692</v>
       </c>
       <c r="R29" t="n">
-        <v>7093717</v>
+        <v>7094117</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3796,12 +3732,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3810,6 +3746,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3827,16 +3764,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116927</t>
+          <t>https://artportalen.se/Sighting/120117729</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120117216</v>
+        <v>120116948</v>
       </c>
       <c r="B30" t="n">
-        <v>58327</v>
+        <v>8444</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3844,27 +3781,32 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103015</v>
+        <v>106554</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3872,10 +3814,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>759669</v>
+        <v>759991</v>
       </c>
       <c r="R30" t="n">
-        <v>7093972</v>
+        <v>7093717</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3902,12 +3844,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3916,8 +3858,29 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3933,16 +3896,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117216</t>
+          <t>https://artportalen.se/Sighting/120116948</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120117228</v>
+        <v>120116961</v>
       </c>
       <c r="B31" t="n">
-        <v>58327</v>
+        <v>99035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3950,27 +3913,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>219790</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3978,10 +3941,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>759719</v>
+        <v>759818</v>
       </c>
       <c r="R31" t="n">
-        <v>7093964</v>
+        <v>7093876</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4022,6 +3985,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4039,16 +4003,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117228</t>
+          <t>https://artportalen.se/Sighting/120116961</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132181706</v>
+        <v>135866265</v>
       </c>
       <c r="B32" t="n">
-        <v>58349</v>
+        <v>99934</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4056,37 +4020,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
+        <v>222306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stjärnstarr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carex echinata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Murray</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sista besöket, Vb</t>
+          <t>Östra skjultfältsvägen, Östra skjultfältsvägen, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>759781</v>
+        <v>759839</v>
       </c>
       <c r="R32" t="n">
-        <v>7093970</v>
+        <v>7093779</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4110,22 +4074,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>16:03</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>16:03</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4140,66 +4094,62 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Tomas Sandström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Tomas Sandström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132181706</t>
+          <t>https://artportalen.se/Sighting/135866265</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120116922</v>
+        <v>115545469</v>
       </c>
       <c r="B33" t="n">
-        <v>58114</v>
+        <v>79515</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>230552</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Långmyrkroken, Långmyrkroken, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>760031</v>
+        <v>759846</v>
       </c>
       <c r="R33" t="n">
-        <v>7093709</v>
+        <v>7093780</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4226,19 +4176,29 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG33" t="b">
         <v>0</v>
@@ -4246,66 +4206,62 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116922</t>
+          <t>https://artportalen.se/Sighting/115545469</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120117299</v>
+        <v>115545471</v>
       </c>
       <c r="B34" t="n">
-        <v>58114</v>
+        <v>79515</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>230552</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Långmyrkroken bb, Långmyrkroken capillaris, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>759645</v>
+        <v>759724</v>
       </c>
       <c r="R34" t="n">
-        <v>7094007</v>
+        <v>7094080</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4332,19 +4288,29 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG34" t="b">
         <v>0</v>
@@ -4352,1477 +4318,16 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/120117299</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>135477724</v>
-      </c>
-      <c r="B35" t="n">
-        <v>58141</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>I20, Vb</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>759733</v>
-      </c>
-      <c r="R35" t="n">
-        <v>7094018</v>
-      </c>
-      <c r="S35" t="n">
-        <v>10</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135477724</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>135477727</v>
-      </c>
-      <c r="B36" t="n">
-        <v>58141</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>I20, Vb</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>759739</v>
-      </c>
-      <c r="R36" t="n">
-        <v>7093883</v>
-      </c>
-      <c r="S36" t="n">
-        <v>5</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135477727</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>120117729</v>
-      </c>
-      <c r="B37" t="n">
-        <v>5199</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>105930</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Vågbandad barkbock</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Semanotus undatus</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Lillklinten, Umeå, Vb</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>759692</v>
-      </c>
-      <c r="R37" t="n">
-        <v>7094117</v>
-      </c>
-      <c r="S37" t="n">
-        <v>25</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="inlineStr"/>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>J-M Roberge</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>J-M Roberge</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/120117729</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>120116948</v>
-      </c>
-      <c r="B38" t="n">
-        <v>8444</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>106554</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Björksplintborre</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Scolytus ratzeburgii</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Lillklinten, Umeå, Vb</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>759991</v>
-      </c>
-      <c r="R38" t="n">
-        <v>7093717</v>
-      </c>
-      <c r="S38" t="n">
-        <v>25</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2024-09-02</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2024-09-02</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>J-M Roberge</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>J-M Roberge</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/120116948</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>120116961</v>
-      </c>
-      <c r="B39" t="n">
-        <v>99035</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>219790</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Dactylorhiza maculata</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Lillklinten, Umeå, Vb</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>759818</v>
-      </c>
-      <c r="R39" t="n">
-        <v>7093876</v>
-      </c>
-      <c r="S39" t="n">
-        <v>25</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="inlineStr"/>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>J-M Roberge</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>J-M Roberge</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/120116961</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>135477716</v>
-      </c>
-      <c r="B40" t="n">
-        <v>99193</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>219790</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Dactylorhiza maculata</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>I20, Vb</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>759825</v>
-      </c>
-      <c r="R40" t="n">
-        <v>7093924</v>
-      </c>
-      <c r="S40" t="n">
-        <v>5</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135477716</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>135477709</v>
-      </c>
-      <c r="B41" t="n">
-        <v>106288</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>221154</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Skogsstjärna</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Lysimachia europaea</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(L.) U. Manns &amp; Anderb.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>I20, Vb</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>759878</v>
-      </c>
-      <c r="R41" t="n">
-        <v>7093775</v>
-      </c>
-      <c r="S41" t="n">
-        <v>12</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135477709</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>135866265</v>
-      </c>
-      <c r="B42" t="n">
-        <v>99934</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>222306</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Stjärnstarr</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Carex echinata</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Murray</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Östra skjultfältsvägen, Östra skjultfältsvägen, Vb</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>759839</v>
-      </c>
-      <c r="R42" t="n">
-        <v>7093779</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Tomas Sandström</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Tomas Sandström</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135866265</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>135477706</v>
-      </c>
-      <c r="B43" t="n">
-        <v>100888</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>222584</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Bergsslok</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Melica nutans</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>I20, Vb</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>760044</v>
-      </c>
-      <c r="R43" t="n">
-        <v>7093709</v>
-      </c>
-      <c r="S43" t="n">
-        <v>5</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135477706</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>135477711</v>
-      </c>
-      <c r="B44" t="n">
-        <v>99082</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>223049</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Ormbär</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Paris quadrifolia</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>I20, Vb</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>759843</v>
-      </c>
-      <c r="R44" t="n">
-        <v>7093832</v>
-      </c>
-      <c r="S44" t="n">
-        <v>5</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135477711</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>135477712</v>
-      </c>
-      <c r="B45" t="n">
-        <v>98327</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>I20, Vb</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>759810</v>
-      </c>
-      <c r="R45" t="n">
-        <v>7093860</v>
-      </c>
-      <c r="S45" t="n">
-        <v>6</v>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AD45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135477712</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>115545469</v>
-      </c>
-      <c r="B46" t="n">
-        <v>79515</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>230552</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Gropig skägglav</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Usnea barbata</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Långmyrkroken, Långmyrkroken, Vb</t>
-        </is>
-      </c>
-      <c r="Q46" t="n">
-        <v>759846</v>
-      </c>
-      <c r="R46" t="n">
-        <v>7093780</v>
-      </c>
-      <c r="S46" t="n">
-        <v>25</v>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AD46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AG46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT46" t="inlineStr"/>
-      <c r="AW46" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/115545469</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>115545471</v>
-      </c>
-      <c r="B47" t="n">
-        <v>79515</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>230552</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Gropig skägglav</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Usnea barbata</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Långmyrkroken bb, Långmyrkroken capillaris, Vb</t>
-        </is>
-      </c>
-      <c r="Q47" t="n">
-        <v>759724</v>
-      </c>
-      <c r="R47" t="n">
-        <v>7094080</v>
-      </c>
-      <c r="S47" t="n">
-        <v>25</v>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AD47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="b">
-        <v>1</v>
-      </c>
-      <c r="AG47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
-      <c r="AZ47" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/115545471</t>
         </is>
@@ -5863,19 +4368,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ34"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115545462</v>
+        <v>135478612</v>
       </c>
       <c r="B4" t="n">
-        <v>79359</v>
+        <v>79473</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långmyrkroken capillaris, Långmyrkroken capillaris, Vb</t>
+          <t>Långmyrkroken, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -945,7 +945,7 @@
         <v>7094082</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,7 +1010,7 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115545462</t>
+          <t>https://artportalen.se/Sighting/135478612</t>
         </is>
       </c>
     </row>
@@ -1796,10 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120117695</v>
+        <v>135477718</v>
       </c>
       <c r="B12" t="n">
-        <v>91872</v>
+        <v>96488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1807,40 +1807,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>2812</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759692</v>
+        <v>759797</v>
       </c>
       <c r="R12" t="n">
-        <v>7094117</v>
+        <v>7093887</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1864,12 +1861,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1878,34 +1885,33 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117695</t>
+          <t>https://artportalen.se/Sighting/135477718</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115544900</v>
+        <v>135477719</v>
       </c>
       <c r="B13" t="n">
-        <v>79351</v>
+        <v>96488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,37 +1919,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6434</v>
+        <v>2812</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långmyrkroken nästlav, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759653</v>
+        <v>759767</v>
       </c>
       <c r="R13" t="n">
-        <v>7093950</v>
+        <v>7093964</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1967,22 +1973,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2008,16 +2014,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115544900</t>
+          <t>https://artportalen.se/Sighting/135477719</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120117311</v>
+        <v>135477737</v>
       </c>
       <c r="B14" t="n">
-        <v>79351</v>
+        <v>92264</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2025,40 +2031,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6434</v>
+        <v>3008</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759623</v>
+        <v>759701</v>
       </c>
       <c r="R14" t="n">
-        <v>7094019</v>
+        <v>7094065</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2082,12 +2085,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>på liggande gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2096,80 +2114,71 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117311</t>
+          <t>https://artportalen.se/Sighting/135477737</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120117194</v>
+        <v>135477725</v>
       </c>
       <c r="B15" t="n">
-        <v>57950</v>
+        <v>89292</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>4412</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>759658</v>
+        <v>759743</v>
       </c>
       <c r="R15" t="n">
-        <v>7093955</v>
+        <v>7093897</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2193,12 +2202,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2213,27 +2232,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117194</t>
+          <t>https://artportalen.se/Sighting/135477725</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120117321</v>
+        <v>120117695</v>
       </c>
       <c r="B16" t="n">
-        <v>57950</v>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2241,31 +2260,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2273,10 +2287,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759730</v>
+        <v>759692</v>
       </c>
       <c r="R16" t="n">
-        <v>7094006</v>
+        <v>7094117</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2317,6 +2331,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2334,16 +2349,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117321</t>
+          <t>https://artportalen.se/Sighting/120117695</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120117422</v>
+        <v>115544900</v>
       </c>
       <c r="B17" t="n">
-        <v>57950</v>
+        <v>79351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2351,42 +2366,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Långmyrkroken nästlav, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759709</v>
+        <v>759653</v>
       </c>
       <c r="R17" t="n">
-        <v>7094089</v>
+        <v>7093950</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2413,12 +2420,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2433,27 +2450,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117422</t>
+          <t>https://artportalen.se/Sighting/115544900</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120117584</v>
+        <v>120117311</v>
       </c>
       <c r="B18" t="n">
-        <v>57950</v>
+        <v>79351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2461,31 +2478,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2493,10 +2505,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759680</v>
+        <v>759623</v>
       </c>
       <c r="R18" t="n">
-        <v>7094134</v>
+        <v>7094019</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2537,6 +2549,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2554,16 +2567,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117584</t>
+          <t>https://artportalen.se/Sighting/120117311</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115545071</v>
+        <v>135477739</v>
       </c>
       <c r="B19" t="n">
-        <v>57141</v>
+        <v>80567</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2571,45 +2584,40 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lillklinten, Lillklinten, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759586</v>
+        <v>759699</v>
       </c>
       <c r="R19" t="n">
-        <v>7094100</v>
+        <v>7094113</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2633,22 +2641,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2657,8 +2665,24 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2674,16 +2698,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115545071</t>
+          <t>https://artportalen.se/Sighting/135477739</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120116985</v>
+        <v>120117194</v>
       </c>
       <c r="B20" t="n">
-        <v>4775</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2691,30 +2715,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2724,10 +2747,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759806</v>
+        <v>759658</v>
       </c>
       <c r="R20" t="n">
-        <v>7093910</v>
+        <v>7093955</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2754,12 +2777,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2768,7 +2791,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2786,16 +2808,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116985</t>
+          <t>https://artportalen.se/Sighting/120117194</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120116996</v>
+        <v>120117321</v>
       </c>
       <c r="B21" t="n">
-        <v>4775</v>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,30 +2825,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2836,10 +2857,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759799</v>
+        <v>759730</v>
       </c>
       <c r="R21" t="n">
-        <v>7093877</v>
+        <v>7094006</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2866,12 +2887,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2880,7 +2901,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2898,16 +2918,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116996</t>
+          <t>https://artportalen.se/Sighting/120117321</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115581059</v>
+        <v>120117422</v>
       </c>
       <c r="B22" t="n">
-        <v>58327</v>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,16 +2935,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2933,16 +2953,24 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lillklinten, Lillklinten, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759635</v>
+        <v>759709</v>
       </c>
       <c r="R22" t="n">
-        <v>7094098</v>
+        <v>7094089</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2969,22 +2997,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>16:27</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>16:27</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2999,27 +3017,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115581059</t>
+          <t>https://artportalen.se/Sighting/120117422</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120116927</v>
+        <v>120117584</v>
       </c>
       <c r="B23" t="n">
-        <v>58327</v>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3027,16 +3045,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3047,7 +3065,11 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3055,10 +3077,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759991</v>
+        <v>759680</v>
       </c>
       <c r="R23" t="n">
-        <v>7093717</v>
+        <v>7094134</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3085,12 +3107,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3116,16 +3138,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116927</t>
+          <t>https://artportalen.se/Sighting/120117584</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120117216</v>
+        <v>115545071</v>
       </c>
       <c r="B24" t="n">
-        <v>58327</v>
+        <v>57141</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3133,38 +3155,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Lillklinten, Lillklinten, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759669</v>
+        <v>759586</v>
       </c>
       <c r="R24" t="n">
-        <v>7093972</v>
+        <v>7094100</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3191,12 +3217,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3211,27 +3247,27 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117216</t>
+          <t>https://artportalen.se/Sighting/115545071</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120117228</v>
+        <v>120116985</v>
       </c>
       <c r="B25" t="n">
-        <v>58327</v>
+        <v>4775</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3239,27 +3275,32 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>100299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3267,10 +3308,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759719</v>
+        <v>759806</v>
       </c>
       <c r="R25" t="n">
-        <v>7093964</v>
+        <v>7093910</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3297,12 +3338,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3311,6 +3352,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3328,16 +3370,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117228</t>
+          <t>https://artportalen.se/Sighting/120116985</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132181706</v>
+        <v>120116996</v>
       </c>
       <c r="B26" t="n">
-        <v>58349</v>
+        <v>4775</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3345,34 +3387,43 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>100299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sista besöket, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759781</v>
+        <v>759799</v>
       </c>
       <c r="R26" t="n">
-        <v>7093970</v>
+        <v>7093877</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3399,22 +3450,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:03</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:03</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3423,75 +3464,72 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132181706</t>
+          <t>https://artportalen.se/Sighting/120116996</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120116922</v>
+        <v>135478598</v>
       </c>
       <c r="B27" t="n">
-        <v>58114</v>
+        <v>5181</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>760031</v>
+        <v>759797</v>
       </c>
       <c r="R27" t="n">
-        <v>7093709</v>
+        <v>7093900</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3515,12 +3553,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3531,70 +3579,81 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116922</t>
+          <t>https://artportalen.se/Sighting/135478598</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120117299</v>
+        <v>115581059</v>
       </c>
       <c r="B28" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Lillklinten, Lillklinten, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>759645</v>
+        <v>759635</v>
       </c>
       <c r="R28" t="n">
-        <v>7094007</v>
+        <v>7094098</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3621,12 +3680,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3641,27 +3710,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117299</t>
+          <t>https://artportalen.se/Sighting/115581059</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120117729</v>
+        <v>120116927</v>
       </c>
       <c r="B29" t="n">
-        <v>5199</v>
+        <v>58327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3669,16 +3738,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3687,14 +3756,9 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3702,10 +3766,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759692</v>
+        <v>759991</v>
       </c>
       <c r="R29" t="n">
-        <v>7094117</v>
+        <v>7093717</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3732,12 +3796,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3746,7 +3810,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3764,16 +3827,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117729</t>
+          <t>https://artportalen.se/Sighting/120116927</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120116948</v>
+        <v>120117216</v>
       </c>
       <c r="B30" t="n">
-        <v>8444</v>
+        <v>58327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3781,32 +3844,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106554</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3814,10 +3872,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>759991</v>
+        <v>759669</v>
       </c>
       <c r="R30" t="n">
-        <v>7093717</v>
+        <v>7093972</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3844,12 +3902,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3858,29 +3916,8 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3896,16 +3933,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116948</t>
+          <t>https://artportalen.se/Sighting/120117216</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120116961</v>
+        <v>120117228</v>
       </c>
       <c r="B31" t="n">
-        <v>99035</v>
+        <v>58327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3913,27 +3950,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219790</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3941,10 +3978,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>759818</v>
+        <v>759719</v>
       </c>
       <c r="R31" t="n">
-        <v>7093876</v>
+        <v>7093964</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3985,7 +4022,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4003,16 +4039,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116961</t>
+          <t>https://artportalen.se/Sighting/120117228</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135866265</v>
+        <v>132181706</v>
       </c>
       <c r="B32" t="n">
-        <v>99934</v>
+        <v>58349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4020,37 +4056,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222306</v>
+        <v>103015</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stjärnstarr</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carex echinata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Murray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Östra skjultfältsvägen, Östra skjultfältsvägen, Vb</t>
+          <t>Sista besöket, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>759839</v>
+        <v>759781</v>
       </c>
       <c r="R32" t="n">
-        <v>7093779</v>
+        <v>7093970</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4074,12 +4110,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4094,62 +4140,66 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Tomas Sandström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tomas Sandström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135866265</t>
+          <t>https://artportalen.se/Sighting/132181706</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>115545469</v>
+        <v>120116922</v>
       </c>
       <c r="B33" t="n">
-        <v>79515</v>
+        <v>58114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>230552</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Långmyrkroken, Långmyrkroken, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>759846</v>
+        <v>760031</v>
       </c>
       <c r="R33" t="n">
-        <v>7093780</v>
+        <v>7093709</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4176,29 +4226,19 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:19</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:19</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="b">
         <v>0</v>
@@ -4206,62 +4246,66 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115545469</t>
+          <t>https://artportalen.se/Sighting/120116922</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>115545471</v>
+        <v>120117299</v>
       </c>
       <c r="B34" t="n">
-        <v>79515</v>
+        <v>58114</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>230552</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Långmyrkroken bb, Långmyrkroken capillaris, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>759724</v>
+        <v>759645</v>
       </c>
       <c r="R34" t="n">
-        <v>7094080</v>
+        <v>7094007</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4288,29 +4332,19 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="b">
         <v>0</v>
@@ -4318,16 +4352,1477 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120117299</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135477724</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>759733</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7094018</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477724</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135477727</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>759739</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7093883</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477727</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120117729</v>
+      </c>
+      <c r="B37" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>759692</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7094117</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120117729</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120116948</v>
+      </c>
+      <c r="B38" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>759991</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7093717</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120116948</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120116961</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>759818</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7093876</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120116961</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135477716</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99193</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>759825</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7093924</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477716</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135477709</v>
+      </c>
+      <c r="B41" t="n">
+        <v>106288</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221154</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Skogsstjärna</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lysimachia europaea</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>759878</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7093775</v>
+      </c>
+      <c r="S41" t="n">
+        <v>12</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477709</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135866265</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99934</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222306</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Stjärnstarr</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Carex echinata</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Murray</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Östra skjultfältsvägen, Östra skjultfältsvägen, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>759839</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7093779</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Tomas Sandström</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Tomas Sandström</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135866265</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135477706</v>
+      </c>
+      <c r="B43" t="n">
+        <v>100888</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>760044</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7093709</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477706</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135477711</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99082</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>759843</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7093832</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477711</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135477712</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98327</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>759810</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7093860</v>
+      </c>
+      <c r="S45" t="n">
+        <v>6</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477712</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>115545469</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79515</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>230552</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Gropig skägglav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Usnea barbata</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Långmyrkroken, Långmyrkroken, Vb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>759846</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7093780</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115545469</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>115545471</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79515</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>230552</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Gropig skägglav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Usnea barbata</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Långmyrkroken bb, Långmyrkroken capillaris, Vb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>759724</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7094080</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/115545471</t>
         </is>
@@ -4368,6 +5863,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ47"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135478612</v>
+        <v>115545462</v>
       </c>
       <c r="B4" t="n">
-        <v>79473</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långmyrkroken, Vb</t>
+          <t>Långmyrkroken capillaris, Långmyrkroken capillaris, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -945,7 +945,7 @@
         <v>7094082</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,7 +1010,7 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135478612</t>
+          <t>https://artportalen.se/Sighting/115545462</t>
         </is>
       </c>
     </row>
@@ -1796,10 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135477718</v>
+        <v>120117695</v>
       </c>
       <c r="B12" t="n">
-        <v>96488</v>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1807,37 +1807,40 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2812</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>I20, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759797</v>
+        <v>759692</v>
       </c>
       <c r="R12" t="n">
-        <v>7093887</v>
+        <v>7094117</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1861,22 +1864,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1885,33 +1878,34 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477718</t>
+          <t>https://artportalen.se/Sighting/120117695</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135477719</v>
+        <v>115544900</v>
       </c>
       <c r="B13" t="n">
-        <v>96488</v>
+        <v>79351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1919,37 +1913,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2812</v>
+        <v>6434</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>I20, Vb</t>
+          <t>Långmyrkroken nästlav, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759767</v>
+        <v>759653</v>
       </c>
       <c r="R13" t="n">
-        <v>7093964</v>
+        <v>7093950</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1973,22 +1967,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,16 +2008,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477719</t>
+          <t>https://artportalen.se/Sighting/115544900</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135477737</v>
+        <v>120117311</v>
       </c>
       <c r="B14" t="n">
-        <v>92264</v>
+        <v>79351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2031,37 +2025,40 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3008</v>
+        <v>6434</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Timmerticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Amyloporia sinuosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Rajchenb. &amp; al.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>I20, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759701</v>
+        <v>759623</v>
       </c>
       <c r="R14" t="n">
-        <v>7094065</v>
+        <v>7094019</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2085,27 +2082,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>på liggande gran</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2114,71 +2096,80 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477737</t>
+          <t>https://artportalen.se/Sighting/120117311</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135477725</v>
+        <v>120117194</v>
       </c>
       <c r="B15" t="n">
-        <v>89292</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4412</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>I20, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>759743</v>
+        <v>759658</v>
       </c>
       <c r="R15" t="n">
-        <v>7093897</v>
+        <v>7093955</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2202,22 +2193,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2232,27 +2213,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477725</t>
+          <t>https://artportalen.se/Sighting/120117194</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120117695</v>
+        <v>120117321</v>
       </c>
       <c r="B16" t="n">
-        <v>91872</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2260,26 +2241,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2287,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759692</v>
+        <v>759730</v>
       </c>
       <c r="R16" t="n">
-        <v>7094117</v>
+        <v>7094006</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2331,7 +2317,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2349,16 +2334,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117695</t>
+          <t>https://artportalen.se/Sighting/120117321</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115544900</v>
+        <v>120117422</v>
       </c>
       <c r="B17" t="n">
-        <v>79351</v>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,34 +2351,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6434</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långmyrkroken nästlav, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759653</v>
+        <v>759709</v>
       </c>
       <c r="R17" t="n">
-        <v>7093950</v>
+        <v>7094089</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2420,22 +2413,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>17:05</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>17:05</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2450,27 +2433,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115544900</t>
+          <t>https://artportalen.se/Sighting/120117422</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120117311</v>
+        <v>120117584</v>
       </c>
       <c r="B18" t="n">
-        <v>79351</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,26 +2461,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6434</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2505,10 +2493,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759623</v>
+        <v>759680</v>
       </c>
       <c r="R18" t="n">
-        <v>7094019</v>
+        <v>7094134</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2549,7 +2537,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2567,16 +2554,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117311</t>
+          <t>https://artportalen.se/Sighting/120117584</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135477739</v>
+        <v>115545071</v>
       </c>
       <c r="B19" t="n">
-        <v>80567</v>
+        <v>57141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2584,40 +2571,45 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6463</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>I20, Vb</t>
+          <t>Lillklinten, Lillklinten, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759699</v>
+        <v>759586</v>
       </c>
       <c r="R19" t="n">
-        <v>7094113</v>
+        <v>7094100</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2641,22 +2633,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2665,24 +2657,8 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2698,16 +2674,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135477739</t>
+          <t>https://artportalen.se/Sighting/115545071</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120117194</v>
+        <v>120116985</v>
       </c>
       <c r="B20" t="n">
-        <v>57950</v>
+        <v>4775</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,29 +2691,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2747,10 +2724,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759658</v>
+        <v>759806</v>
       </c>
       <c r="R20" t="n">
-        <v>7093955</v>
+        <v>7093910</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2777,12 +2754,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2791,6 +2768,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2808,16 +2786,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117194</t>
+          <t>https://artportalen.se/Sighting/120116985</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120117321</v>
+        <v>120116996</v>
       </c>
       <c r="B21" t="n">
-        <v>57950</v>
+        <v>4775</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2825,29 +2803,30 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2857,10 +2836,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759730</v>
+        <v>759799</v>
       </c>
       <c r="R21" t="n">
-        <v>7094006</v>
+        <v>7093877</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2887,12 +2866,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2901,6 +2880,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2918,16 +2898,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117321</t>
+          <t>https://artportalen.se/Sighting/120116996</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120117422</v>
+        <v>115581059</v>
       </c>
       <c r="B22" t="n">
-        <v>57950</v>
+        <v>58327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2935,16 +2915,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2953,24 +2933,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Lillklinten, Lillklinten, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759709</v>
+        <v>759635</v>
       </c>
       <c r="R22" t="n">
-        <v>7094089</v>
+        <v>7094098</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2997,12 +2969,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3017,27 +2999,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117422</t>
+          <t>https://artportalen.se/Sighting/115581059</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120117584</v>
+        <v>120116927</v>
       </c>
       <c r="B23" t="n">
-        <v>57950</v>
+        <v>58327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3045,16 +3027,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3065,11 +3047,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3077,10 +3055,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759680</v>
+        <v>759991</v>
       </c>
       <c r="R23" t="n">
-        <v>7094134</v>
+        <v>7093717</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3107,12 +3085,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3138,16 +3116,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117584</t>
+          <t>https://artportalen.se/Sighting/120116927</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115545071</v>
+        <v>120117216</v>
       </c>
       <c r="B24" t="n">
-        <v>57141</v>
+        <v>58327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3155,42 +3133,38 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lillklinten, Lillklinten, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759586</v>
+        <v>759669</v>
       </c>
       <c r="R24" t="n">
-        <v>7094100</v>
+        <v>7093972</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3217,22 +3191,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>16:53</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>16:53</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3247,27 +3211,27 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115545071</t>
+          <t>https://artportalen.se/Sighting/120117216</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120116985</v>
+        <v>120117228</v>
       </c>
       <c r="B25" t="n">
-        <v>4775</v>
+        <v>58327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3275,32 +3239,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100299</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3308,10 +3267,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759806</v>
+        <v>759719</v>
       </c>
       <c r="R25" t="n">
-        <v>7093910</v>
+        <v>7093964</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3338,12 +3297,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3352,7 +3311,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3370,16 +3328,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116985</t>
+          <t>https://artportalen.se/Sighting/120117228</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120116996</v>
+        <v>132181706</v>
       </c>
       <c r="B26" t="n">
-        <v>4775</v>
+        <v>58349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3387,43 +3345,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100299</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Sista besöket, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759799</v>
+        <v>759781</v>
       </c>
       <c r="R26" t="n">
-        <v>7093877</v>
+        <v>7093970</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3450,12 +3399,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3464,72 +3423,75 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116996</t>
+          <t>https://artportalen.se/Sighting/132181706</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135478598</v>
+        <v>120116922</v>
       </c>
       <c r="B27" t="n">
-        <v>5181</v>
+        <v>58114</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>I20, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>759797</v>
+        <v>760031</v>
       </c>
       <c r="R27" t="n">
-        <v>7093900</v>
+        <v>7093709</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3553,22 +3515,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:38</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:38</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3579,81 +3531,70 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135478598</t>
+          <t>https://artportalen.se/Sighting/120116922</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115581059</v>
+        <v>120117299</v>
       </c>
       <c r="B28" t="n">
-        <v>58327</v>
+        <v>58114</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lillklinten, Lillklinten, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>759635</v>
+        <v>759645</v>
       </c>
       <c r="R28" t="n">
-        <v>7094098</v>
+        <v>7094007</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3680,22 +3621,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>16:27</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>16:27</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3710,27 +3641,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115581059</t>
+          <t>https://artportalen.se/Sighting/120117299</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120116927</v>
+        <v>120117729</v>
       </c>
       <c r="B29" t="n">
-        <v>58327</v>
+        <v>5199</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3738,16 +3669,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103015</v>
+        <v>105930</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3756,9 +3687,14 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3766,10 +3702,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759991</v>
+        <v>759692</v>
       </c>
       <c r="R29" t="n">
-        <v>7093717</v>
+        <v>7094117</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3796,12 +3732,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3810,6 +3746,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3827,16 +3764,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116927</t>
+          <t>https://artportalen.se/Sighting/120117729</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120117216</v>
+        <v>120116948</v>
       </c>
       <c r="B30" t="n">
-        <v>58327</v>
+        <v>8444</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3844,27 +3781,32 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103015</v>
+        <v>106554</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3872,10 +3814,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>759669</v>
+        <v>759991</v>
       </c>
       <c r="R30" t="n">
-        <v>7093972</v>
+        <v>7093717</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3902,12 +3844,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3916,8 +3858,29 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3933,16 +3896,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117216</t>
+          <t>https://artportalen.se/Sighting/120116948</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120117228</v>
+        <v>120116961</v>
       </c>
       <c r="B31" t="n">
-        <v>58327</v>
+        <v>99035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3950,27 +3913,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>219790</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3978,10 +3941,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>759719</v>
+        <v>759818</v>
       </c>
       <c r="R31" t="n">
-        <v>7093964</v>
+        <v>7093876</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4022,6 +3985,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4039,16 +4003,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117228</t>
+          <t>https://artportalen.se/Sighting/120116961</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132181706</v>
+        <v>135866265</v>
       </c>
       <c r="B32" t="n">
-        <v>58349</v>
+        <v>99951</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4056,37 +4020,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
+        <v>222306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stjärnstarr</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carex echinata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Murray</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sista besöket, Vb</t>
+          <t>Östra skjultfältsvägen, Östra skjultfältsvägen, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>759781</v>
+        <v>759839</v>
       </c>
       <c r="R32" t="n">
-        <v>7093970</v>
+        <v>7093779</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4110,22 +4074,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>16:03</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>16:03</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4140,66 +4094,62 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Tomas Sandström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Tomas Sandström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132181706</t>
+          <t>https://artportalen.se/Sighting/135866265</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120116922</v>
+        <v>115545469</v>
       </c>
       <c r="B33" t="n">
-        <v>58114</v>
+        <v>79515</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>230552</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Långmyrkroken, Långmyrkroken, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>760031</v>
+        <v>759846</v>
       </c>
       <c r="R33" t="n">
-        <v>7093709</v>
+        <v>7093780</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4226,19 +4176,29 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG33" t="b">
         <v>0</v>
@@ -4246,66 +4206,62 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116922</t>
+          <t>https://artportalen.se/Sighting/115545469</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120117299</v>
+        <v>115545471</v>
       </c>
       <c r="B34" t="n">
-        <v>58114</v>
+        <v>79515</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>230552</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Långmyrkroken bb, Långmyrkroken capillaris, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>759645</v>
+        <v>759724</v>
       </c>
       <c r="R34" t="n">
-        <v>7094007</v>
+        <v>7094080</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4332,19 +4288,29 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG34" t="b">
         <v>0</v>
@@ -4352,1477 +4318,16 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/120117299</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>135477724</v>
-      </c>
-      <c r="B35" t="n">
-        <v>58141</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>I20, Vb</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>759733</v>
-      </c>
-      <c r="R35" t="n">
-        <v>7094018</v>
-      </c>
-      <c r="S35" t="n">
-        <v>10</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135477724</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>135477727</v>
-      </c>
-      <c r="B36" t="n">
-        <v>58141</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>I20, Vb</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>759739</v>
-      </c>
-      <c r="R36" t="n">
-        <v>7093883</v>
-      </c>
-      <c r="S36" t="n">
-        <v>5</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135477727</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>120117729</v>
-      </c>
-      <c r="B37" t="n">
-        <v>5199</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>105930</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Vågbandad barkbock</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Semanotus undatus</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Lillklinten, Umeå, Vb</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>759692</v>
-      </c>
-      <c r="R37" t="n">
-        <v>7094117</v>
-      </c>
-      <c r="S37" t="n">
-        <v>25</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="inlineStr"/>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>J-M Roberge</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>J-M Roberge</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/120117729</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>120116948</v>
-      </c>
-      <c r="B38" t="n">
-        <v>8444</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>106554</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Björksplintborre</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Scolytus ratzeburgii</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Lillklinten, Umeå, Vb</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>759991</v>
-      </c>
-      <c r="R38" t="n">
-        <v>7093717</v>
-      </c>
-      <c r="S38" t="n">
-        <v>25</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2024-09-02</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2024-09-02</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>J-M Roberge</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>J-M Roberge</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/120116948</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>120116961</v>
-      </c>
-      <c r="B39" t="n">
-        <v>99035</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>219790</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Dactylorhiza maculata</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Lillklinten, Umeå, Vb</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>759818</v>
-      </c>
-      <c r="R39" t="n">
-        <v>7093876</v>
-      </c>
-      <c r="S39" t="n">
-        <v>25</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="inlineStr"/>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>J-M Roberge</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>J-M Roberge</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/120116961</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>135477716</v>
-      </c>
-      <c r="B40" t="n">
-        <v>99193</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>219790</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Dactylorhiza maculata</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>I20, Vb</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>759825</v>
-      </c>
-      <c r="R40" t="n">
-        <v>7093924</v>
-      </c>
-      <c r="S40" t="n">
-        <v>5</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135477716</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>135477709</v>
-      </c>
-      <c r="B41" t="n">
-        <v>106288</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>221154</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Skogsstjärna</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Lysimachia europaea</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(L.) U. Manns &amp; Anderb.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>I20, Vb</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>759878</v>
-      </c>
-      <c r="R41" t="n">
-        <v>7093775</v>
-      </c>
-      <c r="S41" t="n">
-        <v>12</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135477709</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>135866265</v>
-      </c>
-      <c r="B42" t="n">
-        <v>99934</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>222306</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Stjärnstarr</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Carex echinata</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Murray</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Östra skjultfältsvägen, Östra skjultfältsvägen, Vb</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>759839</v>
-      </c>
-      <c r="R42" t="n">
-        <v>7093779</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Tomas Sandström</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Tomas Sandström</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135866265</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>135477706</v>
-      </c>
-      <c r="B43" t="n">
-        <v>100888</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>222584</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Bergsslok</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Melica nutans</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>I20, Vb</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>760044</v>
-      </c>
-      <c r="R43" t="n">
-        <v>7093709</v>
-      </c>
-      <c r="S43" t="n">
-        <v>5</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135477706</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>135477711</v>
-      </c>
-      <c r="B44" t="n">
-        <v>99082</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>223049</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Ormbär</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Paris quadrifolia</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>I20, Vb</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>759843</v>
-      </c>
-      <c r="R44" t="n">
-        <v>7093832</v>
-      </c>
-      <c r="S44" t="n">
-        <v>5</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135477711</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>135477712</v>
-      </c>
-      <c r="B45" t="n">
-        <v>98327</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>I20, Vb</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>759810</v>
-      </c>
-      <c r="R45" t="n">
-        <v>7093860</v>
-      </c>
-      <c r="S45" t="n">
-        <v>6</v>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AD45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135477712</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>115545469</v>
-      </c>
-      <c r="B46" t="n">
-        <v>79515</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>230552</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Gropig skägglav</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Usnea barbata</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Långmyrkroken, Långmyrkroken, Vb</t>
-        </is>
-      </c>
-      <c r="Q46" t="n">
-        <v>759846</v>
-      </c>
-      <c r="R46" t="n">
-        <v>7093780</v>
-      </c>
-      <c r="S46" t="n">
-        <v>25</v>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AD46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AG46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT46" t="inlineStr"/>
-      <c r="AW46" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/115545469</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>115545471</v>
-      </c>
-      <c r="B47" t="n">
-        <v>79515</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>230552</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Gropig skägglav</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Usnea barbata</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Långmyrkroken bb, Långmyrkroken capillaris, Vb</t>
-        </is>
-      </c>
-      <c r="Q47" t="n">
-        <v>759724</v>
-      </c>
-      <c r="R47" t="n">
-        <v>7094080</v>
-      </c>
-      <c r="S47" t="n">
-        <v>25</v>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AD47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="b">
-        <v>1</v>
-      </c>
-      <c r="AG47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
-      <c r="AZ47" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/115545471</t>
         </is>
@@ -5863,19 +4368,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ34"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115545462</v>
+        <v>135478612</v>
       </c>
       <c r="B4" t="n">
-        <v>79359</v>
+        <v>79475</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långmyrkroken capillaris, Långmyrkroken capillaris, Vb</t>
+          <t>Långmyrkroken, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -945,7 +945,7 @@
         <v>7094082</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,7 +1010,7 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115545462</t>
+          <t>https://artportalen.se/Sighting/135478612</t>
         </is>
       </c>
     </row>
@@ -1796,10 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120117695</v>
+        <v>135477718</v>
       </c>
       <c r="B12" t="n">
-        <v>91872</v>
+        <v>96505</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1807,40 +1807,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>2812</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759692</v>
+        <v>759797</v>
       </c>
       <c r="R12" t="n">
-        <v>7094117</v>
+        <v>7093887</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1864,12 +1861,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1878,34 +1885,33 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117695</t>
+          <t>https://artportalen.se/Sighting/135477718</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115544900</v>
+        <v>135477719</v>
       </c>
       <c r="B13" t="n">
-        <v>79351</v>
+        <v>96505</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,37 +1919,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6434</v>
+        <v>2812</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långmyrkroken nästlav, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759653</v>
+        <v>759767</v>
       </c>
       <c r="R13" t="n">
-        <v>7093950</v>
+        <v>7093964</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1967,22 +1973,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2008,16 +2014,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115544900</t>
+          <t>https://artportalen.se/Sighting/135477719</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120117311</v>
+        <v>135477737</v>
       </c>
       <c r="B14" t="n">
-        <v>79351</v>
+        <v>92278</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2025,40 +2031,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6434</v>
+        <v>3008</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759623</v>
+        <v>759701</v>
       </c>
       <c r="R14" t="n">
-        <v>7094019</v>
+        <v>7094065</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2082,12 +2085,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>på liggande gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2096,80 +2114,71 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117311</t>
+          <t>https://artportalen.se/Sighting/135477737</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120117194</v>
+        <v>135477725</v>
       </c>
       <c r="B15" t="n">
-        <v>57950</v>
+        <v>89294</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>4412</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>759658</v>
+        <v>759743</v>
       </c>
       <c r="R15" t="n">
-        <v>7093955</v>
+        <v>7093897</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2193,12 +2202,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2213,27 +2232,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117194</t>
+          <t>https://artportalen.se/Sighting/135477725</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120117321</v>
+        <v>120117695</v>
       </c>
       <c r="B16" t="n">
-        <v>57950</v>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2241,31 +2260,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2273,10 +2287,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759730</v>
+        <v>759692</v>
       </c>
       <c r="R16" t="n">
-        <v>7094006</v>
+        <v>7094117</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2317,6 +2331,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2334,16 +2349,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117321</t>
+          <t>https://artportalen.se/Sighting/120117695</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120117422</v>
+        <v>115544900</v>
       </c>
       <c r="B17" t="n">
-        <v>57950</v>
+        <v>79351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2351,42 +2366,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Långmyrkroken nästlav, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759709</v>
+        <v>759653</v>
       </c>
       <c r="R17" t="n">
-        <v>7094089</v>
+        <v>7093950</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2413,12 +2420,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2433,27 +2450,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117422</t>
+          <t>https://artportalen.se/Sighting/115544900</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120117584</v>
+        <v>120117311</v>
       </c>
       <c r="B18" t="n">
-        <v>57950</v>
+        <v>79351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2461,31 +2478,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2493,10 +2505,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759680</v>
+        <v>759623</v>
       </c>
       <c r="R18" t="n">
-        <v>7094134</v>
+        <v>7094019</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2537,6 +2549,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2554,16 +2567,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117584</t>
+          <t>https://artportalen.se/Sighting/120117311</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115545071</v>
+        <v>135477739</v>
       </c>
       <c r="B19" t="n">
-        <v>57141</v>
+        <v>80569</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2571,45 +2584,40 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lillklinten, Lillklinten, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759586</v>
+        <v>759699</v>
       </c>
       <c r="R19" t="n">
-        <v>7094100</v>
+        <v>7094113</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2633,22 +2641,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2657,8 +2665,24 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2674,16 +2698,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115545071</t>
+          <t>https://artportalen.se/Sighting/135477739</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120116985</v>
+        <v>120117194</v>
       </c>
       <c r="B20" t="n">
-        <v>4775</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2691,30 +2715,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2724,10 +2747,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759806</v>
+        <v>759658</v>
       </c>
       <c r="R20" t="n">
-        <v>7093910</v>
+        <v>7093955</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2754,12 +2777,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2768,7 +2791,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2786,16 +2808,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116985</t>
+          <t>https://artportalen.se/Sighting/120117194</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120116996</v>
+        <v>120117321</v>
       </c>
       <c r="B21" t="n">
-        <v>4775</v>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,30 +2825,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2836,10 +2857,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759799</v>
+        <v>759730</v>
       </c>
       <c r="R21" t="n">
-        <v>7093877</v>
+        <v>7094006</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2866,12 +2887,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2880,7 +2901,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2898,16 +2918,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116996</t>
+          <t>https://artportalen.se/Sighting/120117321</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115581059</v>
+        <v>120117422</v>
       </c>
       <c r="B22" t="n">
-        <v>58327</v>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,16 +2935,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2933,16 +2953,24 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lillklinten, Lillklinten, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759635</v>
+        <v>759709</v>
       </c>
       <c r="R22" t="n">
-        <v>7094098</v>
+        <v>7094089</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2969,22 +2997,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>16:27</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>16:27</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2999,27 +3017,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115581059</t>
+          <t>https://artportalen.se/Sighting/120117422</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120116927</v>
+        <v>120117584</v>
       </c>
       <c r="B23" t="n">
-        <v>58327</v>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3027,16 +3045,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3047,7 +3065,11 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3055,10 +3077,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759991</v>
+        <v>759680</v>
       </c>
       <c r="R23" t="n">
-        <v>7093717</v>
+        <v>7094134</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3085,12 +3107,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3116,16 +3138,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116927</t>
+          <t>https://artportalen.se/Sighting/120117584</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120117216</v>
+        <v>115545071</v>
       </c>
       <c r="B24" t="n">
-        <v>58327</v>
+        <v>57141</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3133,38 +3155,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Lillklinten, Lillklinten, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759669</v>
+        <v>759586</v>
       </c>
       <c r="R24" t="n">
-        <v>7093972</v>
+        <v>7094100</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3191,12 +3217,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3211,27 +3247,27 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117216</t>
+          <t>https://artportalen.se/Sighting/115545071</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120117228</v>
+        <v>120116985</v>
       </c>
       <c r="B25" t="n">
-        <v>58327</v>
+        <v>4775</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3239,27 +3275,32 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>100299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3267,10 +3308,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759719</v>
+        <v>759806</v>
       </c>
       <c r="R25" t="n">
-        <v>7093964</v>
+        <v>7093910</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3297,12 +3338,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3311,6 +3352,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3328,16 +3370,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117228</t>
+          <t>https://artportalen.se/Sighting/120116985</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132181706</v>
+        <v>120116996</v>
       </c>
       <c r="B26" t="n">
-        <v>58349</v>
+        <v>4775</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3345,34 +3387,43 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>100299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sista besöket, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759781</v>
+        <v>759799</v>
       </c>
       <c r="R26" t="n">
-        <v>7093970</v>
+        <v>7093877</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3399,22 +3450,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:03</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:03</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3423,75 +3464,72 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132181706</t>
+          <t>https://artportalen.se/Sighting/120116996</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120116922</v>
+        <v>135478598</v>
       </c>
       <c r="B27" t="n">
-        <v>58114</v>
+        <v>5182</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>I20, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>760031</v>
+        <v>759797</v>
       </c>
       <c r="R27" t="n">
-        <v>7093709</v>
+        <v>7093900</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3515,12 +3553,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3531,70 +3579,81 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116922</t>
+          <t>https://artportalen.se/Sighting/135478598</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120117299</v>
+        <v>115581059</v>
       </c>
       <c r="B28" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lillklinten, Umeå, Vb</t>
+          <t>Lillklinten, Lillklinten, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>759645</v>
+        <v>759635</v>
       </c>
       <c r="R28" t="n">
-        <v>7094007</v>
+        <v>7094098</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3621,12 +3680,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3641,27 +3710,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117299</t>
+          <t>https://artportalen.se/Sighting/115581059</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120117729</v>
+        <v>120116927</v>
       </c>
       <c r="B29" t="n">
-        <v>5199</v>
+        <v>58327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3669,16 +3738,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3687,14 +3756,9 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3702,10 +3766,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759692</v>
+        <v>759991</v>
       </c>
       <c r="R29" t="n">
-        <v>7094117</v>
+        <v>7093717</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3732,12 +3796,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3746,7 +3810,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3764,16 +3827,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120117729</t>
+          <t>https://artportalen.se/Sighting/120116927</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120116948</v>
+        <v>120117216</v>
       </c>
       <c r="B30" t="n">
-        <v>8444</v>
+        <v>58327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3781,32 +3844,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106554</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3814,10 +3872,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>759991</v>
+        <v>759669</v>
       </c>
       <c r="R30" t="n">
-        <v>7093717</v>
+        <v>7093972</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3844,12 +3902,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3858,29 +3916,8 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3896,16 +3933,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116948</t>
+          <t>https://artportalen.se/Sighting/120117216</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120116961</v>
+        <v>120117228</v>
       </c>
       <c r="B31" t="n">
-        <v>99035</v>
+        <v>58327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3913,27 +3950,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219790</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3941,10 +3978,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>759818</v>
+        <v>759719</v>
       </c>
       <c r="R31" t="n">
-        <v>7093876</v>
+        <v>7093964</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3985,7 +4022,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4003,16 +4039,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120116961</t>
+          <t>https://artportalen.se/Sighting/120117228</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135866265</v>
+        <v>132181706</v>
       </c>
       <c r="B32" t="n">
-        <v>99951</v>
+        <v>58349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4020,37 +4056,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222306</v>
+        <v>103015</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stjärnstarr</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carex echinata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Murray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Östra skjultfältsvägen, Östra skjultfältsvägen, Vb</t>
+          <t>Sista besöket, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>759839</v>
+        <v>759781</v>
       </c>
       <c r="R32" t="n">
-        <v>7093779</v>
+        <v>7093970</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4074,12 +4110,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4094,62 +4140,66 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Tomas Sandström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tomas Sandström</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135866265</t>
+          <t>https://artportalen.se/Sighting/132181706</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>115545469</v>
+        <v>120116922</v>
       </c>
       <c r="B33" t="n">
-        <v>79515</v>
+        <v>58114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>230552</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Långmyrkroken, Långmyrkroken, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>759846</v>
+        <v>760031</v>
       </c>
       <c r="R33" t="n">
-        <v>7093780</v>
+        <v>7093709</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4176,29 +4226,19 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:19</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:19</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="b">
         <v>0</v>
@@ -4206,62 +4246,66 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115545469</t>
+          <t>https://artportalen.se/Sighting/120116922</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>115545471</v>
+        <v>120117299</v>
       </c>
       <c r="B34" t="n">
-        <v>79515</v>
+        <v>58114</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>230552</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Långmyrkroken bb, Långmyrkroken capillaris, Vb</t>
+          <t>Lillklinten, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>759724</v>
+        <v>759645</v>
       </c>
       <c r="R34" t="n">
-        <v>7094080</v>
+        <v>7094007</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4288,29 +4332,19 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="b">
         <v>0</v>
@@ -4318,16 +4352,1477 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120117299</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135477724</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58143</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>759733</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7094018</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477724</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135477727</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58143</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>759739</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7093883</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477727</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120117729</v>
+      </c>
+      <c r="B37" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>759692</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7094117</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120117729</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120116948</v>
+      </c>
+      <c r="B38" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>759991</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7093717</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120116948</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120116961</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lillklinten, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>759818</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7093876</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120116961</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135477716</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99210</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>759825</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7093924</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477716</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135477709</v>
+      </c>
+      <c r="B41" t="n">
+        <v>106308</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221154</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Skogsstjärna</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lysimachia europaea</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>759878</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7093775</v>
+      </c>
+      <c r="S41" t="n">
+        <v>12</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477709</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135866265</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99951</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222306</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Stjärnstarr</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Carex echinata</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Murray</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Östra skjultfältsvägen, Östra skjultfältsvägen, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>759839</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7093779</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Tomas Sandström</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Tomas Sandström</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135866265</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135477706</v>
+      </c>
+      <c r="B43" t="n">
+        <v>100905</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>760044</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7093709</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477706</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135477711</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99099</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>759843</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7093832</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477711</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135477712</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98344</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>I20, Vb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>759810</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7093860</v>
+      </c>
+      <c r="S45" t="n">
+        <v>6</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135477712</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>115545469</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79515</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>230552</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Gropig skägglav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Usnea barbata</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Långmyrkroken, Långmyrkroken, Vb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>759846</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7093780</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115545469</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>115545471</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79515</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>230552</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Gropig skägglav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Usnea barbata</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Långmyrkroken bb, Långmyrkroken capillaris, Vb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>759724</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7094080</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/115545471</t>
         </is>
@@ -4368,6 +5863,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>135478612</v>
       </c>
       <c r="B4" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>135477718</v>
       </c>
       <c r="B12" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>135477719</v>
       </c>
       <c r="B13" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>135477737</v>
       </c>
       <c r="B14" t="n">
-        <v>92278</v>
+        <v>92279</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>135477725</v>
       </c>
       <c r="B15" t="n">
-        <v>89294</v>
+        <v>89295</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>135477739</v>
       </c>
       <c r="B19" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>135477716</v>
       </c>
       <c r="B40" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>135477709</v>
       </c>
       <c r="B41" t="n">
-        <v>106308</v>
+        <v>106310</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>135866265</v>
       </c>
       <c r="B42" t="n">
-        <v>99951</v>
+        <v>99953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>135477706</v>
       </c>
       <c r="B43" t="n">
-        <v>100905</v>
+        <v>100907</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>135477711</v>
       </c>
       <c r="B44" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>135477712</v>
       </c>
       <c r="B45" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -5171,7 +5171,7 @@
         <v>135866265</v>
       </c>
       <c r="B42" t="n">
-        <v>99953</v>
+        <v>99954</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -5171,7 +5171,7 @@
         <v>135866265</v>
       </c>
       <c r="B42" t="n">
-        <v>99954</v>
+        <v>99955</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -5171,7 +5171,7 @@
         <v>135866265</v>
       </c>
       <c r="B42" t="n">
-        <v>99955</v>
+        <v>99961</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -5171,7 +5171,7 @@
         <v>135866265</v>
       </c>
       <c r="B42" t="n">
-        <v>99961</v>
+        <v>99962</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -5171,7 +5171,7 @@
         <v>135866265</v>
       </c>
       <c r="B42" t="n">
-        <v>99962</v>
+        <v>99973</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -5171,7 +5171,7 @@
         <v>135866265</v>
       </c>
       <c r="B42" t="n">
-        <v>99973</v>
+        <v>99986</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -5171,7 +5171,7 @@
         <v>135866265</v>
       </c>
       <c r="B42" t="n">
-        <v>99986</v>
+        <v>99987</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -5171,7 +5171,7 @@
         <v>135866265</v>
       </c>
       <c r="B42" t="n">
-        <v>99987</v>
+        <v>100000</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 6725-2024 artfynd.xlsx
+++ b/artfynd/A 6725-2024 artfynd.xlsx
@@ -5171,7 +5171,7 @@
         <v>135866265</v>
       </c>
       <c r="B42" t="n">
-        <v>100000</v>
+        <v>100001</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
